--- a/p/utils/csv_table.xlsx
+++ b/p/utils/csv_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adsv\private\books\language\ingush\Dahkilgov\github\dahkilgov\p\utils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37711A68-796A-4149-8024-7899C65E76D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F513E2FA-453C-4841-A5EA-C88322803CDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-2415" windowWidth="38640" windowHeight="21120" xr2:uid="{09FF60B3-0866-4FB8-9F4D-0BC30783F9C4}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">list!$A$1:$O$172</definedName>
+    <definedName name="ExternalData_1" localSheetId="0" hidden="1">list!$B$1:$P$172</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -175,8 +175,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DC9C4742-36BE-4DC5-B3F7-CE74AFF6535A}" name="list" displayName="list" ref="A1:O173" tableType="queryTable" totalsRowCount="1">
-  <autoFilter ref="A1:O172" xr:uid="{DC9C4742-36BE-4DC5-B3F7-CE74AFF6535A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DC9C4742-36BE-4DC5-B3F7-CE74AFF6535A}" name="list" displayName="list" ref="B1:P173" tableType="queryTable" totalsRowCount="1">
+  <autoFilter ref="B1:P172" xr:uid="{DC9C4742-36BE-4DC5-B3F7-CE74AFF6535A}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{DD8A5A01-3BE3-4527-B926-CF54BFDFBC24}" uniqueName="1" name="Column1" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{87BE8C8C-A7F2-44E3-819D-B036BE31FA15}" uniqueName="2" name="Column2" queryTableFieldId="2"/>
@@ -517,6725 +517,7250 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2286C04B-A12B-463C-9EAA-027CF817C1DA}">
-  <dimension ref="A1:O174"/>
+  <dimension ref="A1:P174"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="9" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="15" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
         <v>270</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>777</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>1356</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>1479</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>1971</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>1974</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>1975</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>1984</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>1993</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>2012</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>2017</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
         <v>403</v>
       </c>
-      <c r="B3">
+      <c r="C3">
         <v>880</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>903</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>1220</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>1250</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>1251</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>1257</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>1348</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>1544</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>1655</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>1834</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
         <v>208</v>
       </c>
-      <c r="B4">
+      <c r="C4">
         <v>396</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>497</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>586</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>708</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>779</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>1266</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>1371</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>1741</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>1742</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>1829</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
         <v>334</v>
       </c>
-      <c r="B5">
+      <c r="C5">
         <v>350</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>391</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>439</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>440</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>551</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>776</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>795</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>1102</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>1488</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>1703</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>1832</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>1853</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>2035</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
         <v>280</v>
       </c>
-      <c r="B6">
+      <c r="C6">
         <v>282</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>291</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>295</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>539</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>729</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>868</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>869</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>871</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>1104</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>1156</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>1543</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>1862</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
         <v>80</v>
       </c>
-      <c r="B7">
+      <c r="C7">
         <v>783</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>784</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>1230</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>1411</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>1471</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>1516</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>1607</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>1651</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>1868</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
         <v>144</v>
       </c>
-      <c r="B8">
+      <c r="C8">
         <v>229</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>232</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>236</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>238</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>246</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>255</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>349</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>494</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>688</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>950</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>1835</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
         <v>40</v>
       </c>
-      <c r="B9">
+      <c r="C9">
         <v>239</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>363</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>464</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>984</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>1293</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>1332</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>1349</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>1461</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>1568</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>1936</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
         <v>231</v>
       </c>
-      <c r="B10">
+      <c r="C10">
         <v>233</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>237</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>243</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>244</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>1109</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>1112</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>1322</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>1945</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>1968</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
         <v>234</v>
       </c>
-      <c r="B11">
+      <c r="C11">
         <v>241</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>322</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>335</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>533</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>962</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>978</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>1222</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>1472</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>1785</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>1983</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>2089</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
         <v>240</v>
       </c>
-      <c r="B12">
+      <c r="C12">
         <v>324</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>959</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>1238</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>1243</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>1499</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>1626</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>1632</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>1942</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>1957</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
         <v>3</v>
       </c>
-      <c r="B13">
+      <c r="C13">
         <v>230</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>1065</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>1141</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>1151</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>1155</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>1164</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>1186</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>1334</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>1507</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>2003</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
         <v>7</v>
       </c>
-      <c r="B14">
+      <c r="C14">
         <v>83</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>261</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>767</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>881</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>1029</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>1115</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>1223</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>1341</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>1582</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>1601</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>1644</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
         <v>247</v>
       </c>
-      <c r="B15">
+      <c r="C15">
         <v>269</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>413</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>506</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>886</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>910</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>1395</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>1895</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>1963</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>2029</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>2057</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>2077</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
         <v>158</v>
       </c>
-      <c r="B16">
+      <c r="C16">
         <v>393</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>430</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>475</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>772</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>813</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>840</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>1026</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>1281</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>1331</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>1526</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>1728</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
         <v>90</v>
       </c>
-      <c r="B17">
+      <c r="C17">
         <v>249</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>383</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>419</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>424</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>1044</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>1119</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>1121</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>1122</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>1124</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>1263</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
         <v>112</v>
       </c>
-      <c r="B18">
+      <c r="C18">
         <v>169</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>517</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>518</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>653</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>687</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>771</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>1030</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>1305</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>1042</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>1043</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>1459</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>1849</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
         <v>36</v>
       </c>
-      <c r="B19">
+      <c r="C19">
         <v>185</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>412</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>425</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>602</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>656</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>839</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>845</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>1665</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>1784</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>1962</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>2083</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
         <v>20</v>
       </c>
-      <c r="B20">
+      <c r="C20">
         <v>159</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>284</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>414</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>737</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>1049</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>1270</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>1579</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>1581</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>1690</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>1990</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>2032</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
         <v>84</v>
       </c>
-      <c r="B21">
+      <c r="C21">
         <v>202</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>307</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>405</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>982</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>1150</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>1603</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>1609</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>1783</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>1881</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>1914</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
         <v>423</v>
       </c>
-      <c r="B22">
+      <c r="C22">
         <v>458</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>603</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>651</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>733</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>742</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>825</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>1031</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>1061</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>1191</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>1216</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>1399</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
         <v>184</v>
       </c>
-      <c r="B23">
+      <c r="C23">
         <v>217</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>258</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>332</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>465</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>467</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>515</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>534</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>986</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>1768</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>2007</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>2042</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>2045</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
         <v>271</v>
       </c>
-      <c r="B24">
+      <c r="C24">
         <v>360</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>713</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>715</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>847</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>851</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>1101</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>1330</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>1474</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>1491</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>1529</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>1612</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>1812</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
         <v>87</v>
       </c>
-      <c r="B25">
+      <c r="C25">
         <v>151</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>487</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>536</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>654</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>756</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>940</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>1506</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>1567</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>1572</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>1638</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>1739</v>
       </c>
-      <c r="M25">
+      <c r="N25">
         <v>1758</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
         <v>75</v>
       </c>
-      <c r="B26">
+      <c r="C26">
         <v>138</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>351</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>353</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>372</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>489</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>608</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>681</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>912</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>1040</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>1103</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>1948</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>2095</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
         <v>76</v>
       </c>
-      <c r="B27">
+      <c r="C27">
         <v>176</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>272</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>273</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>290</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>381</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>426</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>436</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>552</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>1682</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>1691</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>1926</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>2041</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
         <v>429</v>
       </c>
-      <c r="B28">
+      <c r="C28">
         <v>472</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>710</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>716</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>749</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>766</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>768</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>1024</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>1189</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>1289</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>1290</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>1338</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>1413</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>1610</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
         <v>203</v>
       </c>
-      <c r="B29">
+      <c r="C29">
         <v>204</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>447</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>677</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>791</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>792</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>1106</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>1340</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>1513</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>1577</v>
       </c>
-      <c r="K29">
+      <c r="L29">
         <v>1578</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>1908</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
         <v>342</v>
       </c>
-      <c r="B30">
+      <c r="C30">
         <v>523</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>678</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>712</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>730</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>887</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>911</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>922</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>1246</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>1342</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>1345</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>1778</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>2022</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
         <v>205</v>
       </c>
-      <c r="B31">
+      <c r="C31">
         <v>252</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>492</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>541</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>1336</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>1343</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>1384</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>1687</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>1688</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>1696</v>
       </c>
-      <c r="K31">
+      <c r="L31">
         <v>1987</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>2093</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
         <v>373</v>
       </c>
-      <c r="B32">
+      <c r="C32">
         <v>490</v>
       </c>
-      <c r="C32">
+      <c r="D32">
         <v>594</v>
       </c>
-      <c r="D32">
+      <c r="E32">
         <v>920</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <v>1096</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>1344</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>1666</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>1786</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>1808</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>1943</v>
       </c>
-      <c r="K32">
+      <c r="L32">
         <v>2058</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
         <v>394</v>
       </c>
-      <c r="B33">
+      <c r="C33">
         <v>764</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>964</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>1171</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>1302</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>1391</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>1514</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>1586</v>
       </c>
-      <c r="I33">
+      <c r="J33">
         <v>1605</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <v>1618</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>1683</v>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>1804</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
         <v>153</v>
       </c>
-      <c r="B34">
+      <c r="C34">
         <v>194</v>
       </c>
-      <c r="C34">
+      <c r="D34">
         <v>221</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>263</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <v>512</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>529</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>542</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <v>735</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>1170</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>1551</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>1590</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>1753</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
         <v>250</v>
       </c>
-      <c r="B35">
+      <c r="C35">
         <v>299</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>300</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>303</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>306</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>308</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>309</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>574</v>
       </c>
-      <c r="I35">
+      <c r="J35">
         <v>753</v>
       </c>
-      <c r="J35">
+      <c r="K35">
         <v>754</v>
       </c>
-      <c r="K35">
+      <c r="L35">
         <v>930</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>1117</v>
       </c>
-      <c r="M35">
+      <c r="N35">
         <v>1811</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
         <v>73</v>
       </c>
-      <c r="B36">
+      <c r="C36">
         <v>206</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>216</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>501</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>527</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>968</v>
       </c>
-      <c r="G36">
+      <c r="H36">
+        <v>1027</v>
+      </c>
+      <c r="I36">
         <v>1482</v>
       </c>
-      <c r="H36">
+      <c r="J36">
+        <v>1556</v>
+      </c>
+      <c r="K36">
         <v>1902</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
         <v>94</v>
       </c>
-      <c r="B37">
+      <c r="C37">
         <v>122</v>
       </c>
-      <c r="C37">
+      <c r="D37">
         <v>139</v>
       </c>
-      <c r="D37">
+      <c r="E37">
         <v>140</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>544</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>564</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>696</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>1351</v>
       </c>
-      <c r="I37">
+      <c r="J37">
         <v>1377</v>
       </c>
-      <c r="J37">
+      <c r="K37">
         <v>1433</v>
       </c>
-      <c r="K37">
+      <c r="L37">
         <v>1761</v>
       </c>
-      <c r="L37">
+      <c r="M37">
         <v>2097</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
         <v>69</v>
       </c>
-      <c r="B38">
+      <c r="C38">
         <v>71</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <v>156</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>457</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>461</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>462</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>599</v>
       </c>
-      <c r="H38">
+      <c r="I38">
         <v>774</v>
       </c>
-      <c r="I38">
+      <c r="J38">
         <v>1328</v>
       </c>
-      <c r="J38">
+      <c r="K38">
         <v>1781</v>
       </c>
-      <c r="K38">
+      <c r="L38">
         <v>1882</v>
       </c>
-      <c r="L38">
+      <c r="M38">
         <v>1947</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
         <v>325</v>
       </c>
-      <c r="B39">
+      <c r="C39">
         <v>585</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>822</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>953</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>1172</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>1780</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>1816</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>1819</v>
       </c>
-      <c r="I39">
+      <c r="J39">
         <v>1825</v>
       </c>
-      <c r="J39">
+      <c r="K39">
         <v>1843</v>
       </c>
-      <c r="K39">
+      <c r="L39">
         <v>1890</v>
       </c>
-      <c r="L39">
+      <c r="M39">
         <v>1946</v>
       </c>
-      <c r="M39">
+      <c r="N39">
         <v>2091</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
         <v>127</v>
       </c>
-      <c r="B40">
+      <c r="C40">
         <v>225</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>580</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>893</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>925</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>1053</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>1143</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>1422</v>
       </c>
-      <c r="I40">
+      <c r="J40">
         <v>1423</v>
       </c>
-      <c r="J40">
+      <c r="K40">
         <v>1460</v>
       </c>
-      <c r="K40">
+      <c r="L40">
         <v>1548</v>
       </c>
-      <c r="L40">
+      <c r="M40">
         <v>1699</v>
       </c>
-      <c r="M40">
+      <c r="N40">
         <v>1818</v>
       </c>
-      <c r="N40">
+      <c r="O40">
         <v>1871</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
         <v>25</v>
       </c>
-      <c r="B41">
+      <c r="C41">
         <v>147</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>404</v>
       </c>
-      <c r="D41">
+      <c r="E41">
         <v>454</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>486</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <v>695</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>966</v>
       </c>
-      <c r="H41">
+      <c r="I41">
         <v>1273</v>
       </c>
-      <c r="I41">
+      <c r="J41">
         <v>1304</v>
       </c>
-      <c r="J41">
+      <c r="K41">
         <v>1658</v>
       </c>
-      <c r="K41">
+      <c r="L41">
         <v>2074</v>
       </c>
-      <c r="L41">
+      <c r="M41">
         <v>2088</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
         <v>163</v>
       </c>
-      <c r="B42">
+      <c r="C42">
         <v>242</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>491</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>686</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>794</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>1625</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>1650</v>
       </c>
-      <c r="H42">
+      <c r="I42">
         <v>1722</v>
       </c>
-      <c r="I42">
+      <c r="J42">
         <v>1723</v>
       </c>
-      <c r="J42">
+      <c r="K42">
         <v>1730</v>
       </c>
-      <c r="K42">
+      <c r="L42">
         <v>1915</v>
       </c>
-      <c r="L42">
+      <c r="M42">
         <v>2081</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
         <v>33</v>
       </c>
-      <c r="B43">
+      <c r="C43">
         <v>65</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>154</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>641</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>787</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>801</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>1060</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>1092</v>
       </c>
-      <c r="I43">
+      <c r="J43">
         <v>1378</v>
       </c>
-      <c r="J43">
+      <c r="K43">
         <v>1511</v>
       </c>
-      <c r="K43">
+      <c r="L43">
         <v>2062</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
         <v>566</v>
       </c>
-      <c r="B44">
+      <c r="C44">
         <v>568</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>569</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>592</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>618</v>
       </c>
-      <c r="F44">
+      <c r="G44">
         <v>763</v>
       </c>
-      <c r="G44">
+      <c r="H44">
         <v>915</v>
       </c>
-      <c r="H44">
+      <c r="I44">
         <v>979</v>
       </c>
-      <c r="I44">
+      <c r="J44">
         <v>1159</v>
       </c>
-      <c r="J44">
+      <c r="K44">
         <v>1357</v>
       </c>
-      <c r="K44">
+      <c r="L44">
         <v>1719</v>
       </c>
-      <c r="L44">
+      <c r="M44">
         <v>1867</v>
       </c>
-      <c r="M44">
+      <c r="N44">
         <v>2004</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
         <v>265</v>
       </c>
-      <c r="B45">
+      <c r="C45">
         <v>448</v>
       </c>
-      <c r="C45">
+      <c r="D45">
         <v>788</v>
       </c>
-      <c r="D45">
+      <c r="E45">
         <v>957</v>
       </c>
-      <c r="E45">
+      <c r="F45">
         <v>1175</v>
       </c>
-      <c r="F45">
+      <c r="G45">
         <v>1347</v>
       </c>
-      <c r="G45">
+      <c r="H45">
         <v>1848</v>
       </c>
-      <c r="H45">
+      <c r="I45">
         <v>1855</v>
       </c>
-      <c r="I45">
+      <c r="J45">
         <v>1857</v>
       </c>
-      <c r="J45">
+      <c r="K45">
         <v>2071</v>
       </c>
-      <c r="K45">
+      <c r="L45">
         <v>2080</v>
       </c>
-      <c r="L45">
+      <c r="M45">
         <v>2086</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
         <v>120</v>
       </c>
-      <c r="B46">
+      <c r="C46">
         <v>313</v>
       </c>
-      <c r="C46">
+      <c r="D46">
         <v>384</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>385</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>554</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <v>555</v>
       </c>
-      <c r="G46">
+      <c r="H46">
         <v>693</v>
       </c>
-      <c r="H46">
+      <c r="I46">
         <v>1767</v>
       </c>
-      <c r="I46">
+      <c r="J46">
         <v>1776</v>
       </c>
-      <c r="J46">
+      <c r="K46">
         <v>1858</v>
       </c>
-      <c r="K46">
+      <c r="L46">
         <v>1933</v>
       </c>
-      <c r="L46">
+      <c r="M46">
         <v>2098</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
         <v>16</v>
       </c>
-      <c r="B47">
+      <c r="C47">
         <v>550</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>718</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>719</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>720</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>829</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>1492</v>
       </c>
-      <c r="H47">
+      <c r="I47">
         <v>1550</v>
       </c>
-      <c r="I47">
+      <c r="J47">
         <v>1717</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K47">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
         <v>100</v>
       </c>
-      <c r="B48">
+      <c r="C48">
         <v>228</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>376</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>926</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>963</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>1001</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>1017</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>1047</v>
       </c>
-      <c r="I48">
+      <c r="J48">
         <v>1468</v>
       </c>
-      <c r="J48">
+      <c r="K48">
         <v>1489</v>
       </c>
-      <c r="K48">
+      <c r="L48">
         <v>1540</v>
       </c>
-      <c r="L48">
+      <c r="M48">
         <v>1639</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
         <v>178</v>
       </c>
-      <c r="B49">
+      <c r="C49">
         <v>755</v>
       </c>
-      <c r="C49">
+      <c r="D49">
         <v>806</v>
       </c>
-      <c r="D49">
+      <c r="E49">
         <v>909</v>
       </c>
-      <c r="E49">
+      <c r="F49">
         <v>931</v>
       </c>
-      <c r="F49">
+      <c r="G49">
         <v>1379</v>
       </c>
-      <c r="G49">
+      <c r="H49">
         <v>1450</v>
       </c>
-      <c r="H49">
+      <c r="I49">
         <v>1519</v>
       </c>
-      <c r="I49">
+      <c r="J49">
         <v>1621</v>
       </c>
-      <c r="J49">
+      <c r="K49">
         <v>1930</v>
       </c>
-      <c r="K49">
+      <c r="L49">
         <v>2072</v>
       </c>
-      <c r="L49">
+      <c r="M49">
         <v>2079</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
         <v>8</v>
       </c>
-      <c r="B50">
+      <c r="C50">
         <v>132</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>852</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>992</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>1057</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>1367</v>
       </c>
-      <c r="G50">
+      <c r="H50">
         <v>1523</v>
       </c>
-      <c r="H50">
+      <c r="I50">
         <v>1652</v>
       </c>
-      <c r="I50">
+      <c r="J50">
         <v>1709</v>
       </c>
-      <c r="J50">
+      <c r="K50">
         <v>1939</v>
       </c>
-      <c r="K50">
+      <c r="L50">
         <v>1958</v>
       </c>
-      <c r="L50">
+      <c r="M50">
         <v>2076</v>
       </c>
-      <c r="M50">
+      <c r="N50">
         <v>2090</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
         <v>86</v>
       </c>
-      <c r="B51">
+      <c r="C51">
         <v>222</v>
       </c>
-      <c r="C51">
+      <c r="D51">
         <v>773</v>
       </c>
-      <c r="D51">
+      <c r="E51">
         <v>1072</v>
       </c>
-      <c r="E51">
+      <c r="F51">
         <v>1352</v>
       </c>
-      <c r="F51">
+      <c r="G51">
         <v>1380</v>
       </c>
-      <c r="G51">
+      <c r="H51">
         <v>1803</v>
       </c>
-      <c r="H51">
+      <c r="I51">
         <v>1814</v>
       </c>
-      <c r="I51">
+      <c r="J51">
         <v>1854</v>
       </c>
-      <c r="J51">
+      <c r="K51">
         <v>1886</v>
       </c>
-      <c r="K51">
+      <c r="L51">
         <v>1940</v>
       </c>
-      <c r="L51">
+      <c r="M51">
         <v>1941</v>
       </c>
-      <c r="M51">
+      <c r="N51">
         <v>2033</v>
       </c>
-      <c r="N51">
+      <c r="O51">
         <v>2038</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
         <v>119</v>
       </c>
-      <c r="B52">
+      <c r="C52">
         <v>248</v>
       </c>
-      <c r="C52">
+      <c r="D52">
         <v>266</v>
       </c>
-      <c r="D52">
+      <c r="E52">
         <v>340</v>
       </c>
-      <c r="E52">
+      <c r="F52">
         <v>824</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <v>1035</v>
       </c>
-      <c r="G52">
+      <c r="H52">
         <v>1036</v>
       </c>
-      <c r="H52">
+      <c r="I52">
         <v>1080</v>
       </c>
-      <c r="I52">
+      <c r="J52">
         <v>1225</v>
       </c>
-      <c r="J52">
+      <c r="K52">
         <v>1256</v>
       </c>
-      <c r="K52">
+      <c r="L52">
         <v>1750</v>
       </c>
-      <c r="L52">
+      <c r="M52">
         <v>1756</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53">
         <v>66</v>
       </c>
-      <c r="B53">
+      <c r="C53">
         <v>67</v>
       </c>
-      <c r="C53">
+      <c r="D53">
         <v>68</v>
       </c>
-      <c r="D53">
+      <c r="E53">
         <v>70</v>
       </c>
-      <c r="E53">
+      <c r="F53">
         <v>106</v>
       </c>
-      <c r="F53">
+      <c r="G53">
         <v>589</v>
       </c>
-      <c r="G53">
+      <c r="H53">
         <v>692</v>
       </c>
-      <c r="H53">
+      <c r="I53">
         <v>1254</v>
       </c>
-      <c r="I53">
+      <c r="J53">
         <v>1376</v>
       </c>
-      <c r="J53">
+      <c r="K53">
         <v>1402</v>
       </c>
-      <c r="K53">
+      <c r="L53">
         <v>1508</v>
       </c>
-      <c r="L53">
+      <c r="M53">
         <v>1561</v>
       </c>
-      <c r="M53">
+      <c r="N53">
         <v>1734</v>
       </c>
-      <c r="N53">
+      <c r="O53">
         <v>1807</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
         <v>72</v>
       </c>
-      <c r="B54">
+      <c r="C54">
         <v>268</v>
       </c>
-      <c r="C54">
+      <c r="D54">
         <v>627</v>
       </c>
-      <c r="D54">
+      <c r="E54">
         <v>682</v>
       </c>
-      <c r="E54">
+      <c r="F54">
         <v>711</v>
       </c>
-      <c r="F54">
+      <c r="G54">
         <v>859</v>
       </c>
-      <c r="G54">
+      <c r="H54">
         <v>969</v>
       </c>
-      <c r="H54">
+      <c r="I54">
         <v>996</v>
       </c>
-      <c r="I54">
+      <c r="J54">
         <v>1361</v>
       </c>
-      <c r="J54">
+      <c r="K54">
         <v>1487</v>
       </c>
-      <c r="K54">
+      <c r="L54">
         <v>1611</v>
       </c>
-      <c r="L54">
+      <c r="M54">
         <v>1830</v>
       </c>
-      <c r="M54">
+      <c r="N54">
         <v>1850</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55">
         <v>14</v>
       </c>
-      <c r="B55">
+      <c r="C55">
         <v>105</v>
       </c>
-      <c r="C55">
+      <c r="D55">
         <v>361</v>
       </c>
-      <c r="D55">
+      <c r="E55">
         <v>411</v>
       </c>
-      <c r="E55">
+      <c r="F55">
         <v>636</v>
       </c>
-      <c r="F55">
+      <c r="G55">
         <v>838</v>
       </c>
-      <c r="G55">
+      <c r="H55">
         <v>878</v>
       </c>
-      <c r="H55">
+      <c r="I55">
         <v>1486</v>
       </c>
-      <c r="I55">
+      <c r="J55">
         <v>1736</v>
       </c>
-      <c r="J55">
+      <c r="K55">
         <v>1745</v>
       </c>
-      <c r="K55">
+      <c r="L55">
         <v>1828</v>
       </c>
-      <c r="L55">
+      <c r="M55">
         <v>2009</v>
       </c>
-      <c r="M55">
+      <c r="N55">
         <v>2019</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56">
         <v>28</v>
       </c>
-      <c r="B56">
+      <c r="C56">
         <v>172</v>
       </c>
-      <c r="C56">
+      <c r="D56">
         <v>503</v>
       </c>
-      <c r="D56">
+      <c r="E56">
         <v>508</v>
       </c>
-      <c r="E56">
+      <c r="F56">
         <v>864</v>
       </c>
-      <c r="F56">
+      <c r="G56">
         <v>1087</v>
       </c>
-      <c r="G56">
+      <c r="H56">
         <v>1089</v>
       </c>
-      <c r="H56">
+      <c r="I56">
         <v>1090</v>
       </c>
-      <c r="I56">
+      <c r="J56">
         <v>1205</v>
       </c>
-      <c r="J56">
+      <c r="K56">
         <v>1229</v>
       </c>
-      <c r="K56">
+      <c r="L56">
         <v>1311</v>
       </c>
-      <c r="L56">
+      <c r="M56">
         <v>1432</v>
       </c>
-      <c r="M56">
+      <c r="N56">
         <v>1718</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57">
         <v>41</v>
       </c>
-      <c r="B57">
+      <c r="C57">
         <v>408</v>
       </c>
-      <c r="C57">
+      <c r="D57">
         <v>450</v>
       </c>
-      <c r="D57">
+      <c r="E57">
         <v>528</v>
       </c>
-      <c r="E57">
+      <c r="F57">
         <v>638</v>
       </c>
-      <c r="F57">
+      <c r="G57">
         <v>660</v>
       </c>
-      <c r="G57">
+      <c r="H57">
         <v>883</v>
       </c>
-      <c r="H57">
+      <c r="I57">
         <v>1138</v>
       </c>
-      <c r="I57">
+      <c r="J57">
         <v>1438</v>
       </c>
-      <c r="J57">
+      <c r="K57">
         <v>1444</v>
       </c>
-      <c r="K57">
+      <c r="L57">
         <v>1732</v>
       </c>
-      <c r="L57">
+      <c r="M57">
         <v>2075</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58">
         <v>129</v>
       </c>
-      <c r="B58">
+      <c r="C58">
         <v>171</v>
       </c>
-      <c r="C58">
+      <c r="D58">
         <v>504</v>
       </c>
-      <c r="D58">
+      <c r="E58">
         <v>576</v>
       </c>
-      <c r="E58">
+      <c r="F58">
         <v>584</v>
       </c>
-      <c r="F58">
+      <c r="G58">
         <v>664</v>
       </c>
-      <c r="G58">
+      <c r="H58">
         <v>1127</v>
       </c>
-      <c r="H58">
+      <c r="I58">
         <v>1153</v>
       </c>
-      <c r="I58">
+      <c r="J58">
         <v>1158</v>
       </c>
-      <c r="J58">
+      <c r="K58">
         <v>1922</v>
       </c>
-      <c r="K58">
+      <c r="L58">
         <v>1973</v>
       </c>
-      <c r="L58">
+      <c r="M58">
         <v>2050</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59">
         <v>498</v>
       </c>
-      <c r="B59">
+      <c r="C59">
         <v>507</v>
       </c>
-      <c r="C59">
+      <c r="D59">
         <v>524</v>
       </c>
-      <c r="D59">
+      <c r="E59">
         <v>835</v>
       </c>
-      <c r="E59">
+      <c r="F59">
         <v>956</v>
       </c>
-      <c r="F59">
+      <c r="G59">
         <v>1182</v>
       </c>
-      <c r="G59">
+      <c r="H59">
         <v>1235</v>
       </c>
-      <c r="H59">
+      <c r="I59">
         <v>1253</v>
       </c>
-      <c r="I59">
+      <c r="J59">
         <v>1415</v>
       </c>
-      <c r="J59">
+      <c r="K59">
         <v>1542</v>
       </c>
-      <c r="K59">
+      <c r="L59">
         <v>1706</v>
       </c>
-      <c r="L59">
+      <c r="M59">
         <v>1841</v>
       </c>
-      <c r="M59">
+      <c r="N59">
         <v>1901</v>
       </c>
-      <c r="N59">
+      <c r="O59">
         <v>2060</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60">
         <v>379</v>
       </c>
-      <c r="B60">
+      <c r="C60">
         <v>558</v>
       </c>
-      <c r="C60">
+      <c r="D60">
         <v>561</v>
       </c>
-      <c r="D60">
+      <c r="E60">
         <v>1123</v>
       </c>
-      <c r="E60">
+      <c r="F60">
         <v>1259</v>
       </c>
-      <c r="F60">
+      <c r="G60">
         <v>1375</v>
       </c>
-      <c r="G60">
+      <c r="H60">
         <v>1470</v>
       </c>
-      <c r="H60">
+      <c r="I60">
         <v>1596</v>
       </c>
-      <c r="I60">
+      <c r="J60">
         <v>1684</v>
       </c>
-      <c r="J60">
+      <c r="K60">
         <v>1889</v>
       </c>
-      <c r="K60">
+      <c r="L60">
         <v>1921</v>
       </c>
-      <c r="L60">
+      <c r="M60">
         <v>2085</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61">
         <v>170</v>
       </c>
-      <c r="B61">
+      <c r="C61">
         <v>210</v>
       </c>
-      <c r="C61">
+      <c r="D61">
         <v>294</v>
       </c>
-      <c r="D61">
+      <c r="E61">
         <v>867</v>
       </c>
-      <c r="E61">
+      <c r="F61">
         <v>872</v>
       </c>
-      <c r="F61">
+      <c r="G61">
         <v>1195</v>
       </c>
-      <c r="G61">
+      <c r="H61">
         <v>1232</v>
       </c>
-      <c r="H61">
+      <c r="I61">
         <v>1247</v>
       </c>
-      <c r="I61">
+      <c r="J61">
         <v>1269</v>
       </c>
-      <c r="J61">
+      <c r="K61">
         <v>1769</v>
       </c>
-      <c r="K61">
+      <c r="L61">
         <v>1772</v>
       </c>
-      <c r="L61">
+      <c r="M61">
         <v>1872</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62">
         <v>91</v>
       </c>
-      <c r="B62">
+      <c r="C62">
         <v>369</v>
       </c>
-      <c r="C62">
+      <c r="D62">
         <v>827</v>
       </c>
-      <c r="D62">
+      <c r="E62">
         <v>856</v>
       </c>
-      <c r="E62">
+      <c r="F62">
         <v>951</v>
       </c>
-      <c r="F62">
+      <c r="G62">
         <v>1022</v>
       </c>
-      <c r="G62">
+      <c r="H62">
         <v>1298</v>
       </c>
-      <c r="H62">
+      <c r="I62">
         <v>1532</v>
       </c>
-      <c r="I62">
+      <c r="J62">
         <v>1537</v>
       </c>
-      <c r="J62">
+      <c r="K62">
         <v>1647</v>
       </c>
-      <c r="K62">
+      <c r="L62">
         <v>1738</v>
       </c>
-      <c r="L62">
+      <c r="M62">
         <v>1752</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63">
         <v>989</v>
       </c>
-      <c r="B63">
+      <c r="C63">
         <v>1052</v>
       </c>
-      <c r="C63">
+      <c r="D63">
         <v>1346</v>
       </c>
-      <c r="D63">
+      <c r="E63">
         <v>1358</v>
       </c>
-      <c r="E63">
+      <c r="F63">
         <v>1359</v>
       </c>
-      <c r="F63">
+      <c r="G63">
         <v>1407</v>
       </c>
-      <c r="G63">
+      <c r="H63">
         <v>1408</v>
       </c>
-      <c r="H63">
+      <c r="I63">
         <v>1536</v>
       </c>
-      <c r="I63">
+      <c r="J63">
         <v>1547</v>
       </c>
-      <c r="J63">
+      <c r="K63">
         <v>2055</v>
       </c>
-      <c r="K63">
+      <c r="L63">
         <v>2059</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64">
         <v>0</v>
       </c>
-      <c r="B64">
+      <c r="C64">
         <v>302</v>
       </c>
-      <c r="C64">
+      <c r="D64">
         <v>473</v>
       </c>
-      <c r="D64">
+      <c r="E64">
         <v>714</v>
       </c>
-      <c r="E64">
+      <c r="F64">
         <v>906</v>
       </c>
-      <c r="F64">
+      <c r="G64">
         <v>1076</v>
       </c>
-      <c r="G64">
+      <c r="H64">
         <v>1134</v>
       </c>
-      <c r="H64">
+      <c r="I64">
         <v>1149</v>
       </c>
-      <c r="I64">
+      <c r="J64">
         <v>1168</v>
       </c>
-      <c r="J64">
+      <c r="K64">
         <v>1207</v>
       </c>
-      <c r="K64">
+      <c r="L64">
         <v>1821</v>
       </c>
-      <c r="L64">
+      <c r="M64">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65">
         <v>19</v>
       </c>
-      <c r="B65">
+      <c r="C65">
         <v>52</v>
       </c>
-      <c r="C65">
+      <c r="D65">
         <v>134</v>
       </c>
-      <c r="D65">
+      <c r="E65">
         <v>136</v>
       </c>
-      <c r="E65">
+      <c r="F65">
         <v>286</v>
       </c>
-      <c r="F65">
+      <c r="G65">
         <v>365</v>
       </c>
-      <c r="G65">
+      <c r="H65">
         <v>502</v>
       </c>
-      <c r="H65">
+      <c r="I65">
         <v>615</v>
       </c>
-      <c r="I65">
+      <c r="J65">
         <v>667</v>
       </c>
-      <c r="J65">
+      <c r="K65">
         <v>1277</v>
       </c>
-      <c r="K65">
+      <c r="L65">
         <v>1421</v>
       </c>
-      <c r="L65">
+      <c r="M65">
         <v>1439</v>
       </c>
-      <c r="M65">
+      <c r="N65">
         <v>1589</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66">
         <v>128</v>
       </c>
-      <c r="B66">
+      <c r="C66">
         <v>276</v>
       </c>
-      <c r="C66">
+      <c r="D66">
         <v>285</v>
       </c>
-      <c r="D66">
+      <c r="E66">
         <v>521</v>
       </c>
-      <c r="E66">
+      <c r="F66">
         <v>778</v>
       </c>
-      <c r="F66">
+      <c r="G66">
         <v>1064</v>
       </c>
-      <c r="G66">
+      <c r="H66">
         <v>1084</v>
       </c>
-      <c r="H66">
+      <c r="I66">
+        <v>1405</v>
+      </c>
+      <c r="J66">
         <v>1517</v>
       </c>
-      <c r="I66">
+      <c r="K66">
         <v>1911</v>
       </c>
-      <c r="J66">
+      <c r="L66">
         <v>1927</v>
       </c>
-      <c r="K66">
+      <c r="M66">
         <v>2092</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67">
         <v>37</v>
       </c>
-      <c r="B67">
+      <c r="C67">
         <v>364</v>
       </c>
-      <c r="C67">
+      <c r="D67">
         <v>434</v>
       </c>
-      <c r="D67">
+      <c r="E67">
         <v>444</v>
       </c>
-      <c r="E67">
+      <c r="F67">
         <v>456</v>
       </c>
-      <c r="F67">
+      <c r="G67">
         <v>505</v>
       </c>
-      <c r="G67">
+      <c r="H67">
         <v>538</v>
       </c>
-      <c r="H67">
+      <c r="I67">
         <v>543</v>
       </c>
-      <c r="I67">
+      <c r="J67">
         <v>855</v>
       </c>
-      <c r="J67">
+      <c r="K67">
         <v>1874</v>
       </c>
-      <c r="K67">
+      <c r="L67">
         <v>1998</v>
       </c>
-      <c r="L67">
+      <c r="M67">
         <v>2064</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68">
         <v>26</v>
       </c>
-      <c r="B68">
+      <c r="C68">
         <v>88</v>
       </c>
-      <c r="C68">
+      <c r="D68">
         <v>182</v>
       </c>
-      <c r="D68">
+      <c r="E68">
         <v>289</v>
       </c>
-      <c r="E68">
+      <c r="F68">
         <v>410</v>
       </c>
-      <c r="F68">
+      <c r="G68">
         <v>532</v>
       </c>
-      <c r="G68">
+      <c r="H68">
         <v>540</v>
       </c>
-      <c r="H68">
+      <c r="I68">
         <v>572</v>
       </c>
-      <c r="I68">
+      <c r="J68">
         <v>889</v>
       </c>
-      <c r="J68">
+      <c r="K68">
         <v>1019</v>
       </c>
-      <c r="K68">
+      <c r="L68">
         <v>1296</v>
       </c>
-      <c r="L68">
+      <c r="M68">
         <v>1640</v>
       </c>
-      <c r="M68">
+      <c r="N68">
         <v>1641</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69">
         <v>59</v>
       </c>
-      <c r="B69">
+      <c r="C69">
         <v>382</v>
       </c>
-      <c r="C69">
+      <c r="D69">
         <v>531</v>
       </c>
-      <c r="D69">
+      <c r="E69">
         <v>902</v>
       </c>
-      <c r="E69">
+      <c r="F69">
         <v>1199</v>
       </c>
-      <c r="F69">
+      <c r="G69">
         <v>1310</v>
       </c>
-      <c r="G69">
+      <c r="H69">
         <v>1339</v>
       </c>
-      <c r="H69">
+      <c r="I69">
         <v>1393</v>
       </c>
-      <c r="I69">
+      <c r="J69">
         <v>1695</v>
       </c>
-      <c r="J69">
+      <c r="K69">
         <v>1711</v>
       </c>
-      <c r="K69">
+      <c r="L69">
         <v>1779</v>
       </c>
-      <c r="L69">
+      <c r="M69">
         <v>1801</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70">
         <v>38</v>
       </c>
-      <c r="B70">
+      <c r="C70">
         <v>722</v>
       </c>
-      <c r="C70">
+      <c r="D70">
         <v>817</v>
       </c>
-      <c r="D70">
+      <c r="E70">
         <v>833</v>
       </c>
-      <c r="E70">
+      <c r="F70">
         <v>974</v>
       </c>
-      <c r="F70">
+      <c r="G70">
         <v>1037</v>
       </c>
-      <c r="G70">
+      <c r="H70">
         <v>1082</v>
       </c>
-      <c r="H70">
+      <c r="I70">
         <v>1606</v>
       </c>
-      <c r="I70">
+      <c r="J70">
         <v>1631</v>
       </c>
-      <c r="J70">
+      <c r="K70">
         <v>1633</v>
       </c>
-      <c r="K70">
+      <c r="L70">
         <v>1924</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71">
         <v>23</v>
       </c>
-      <c r="B71">
+      <c r="C71">
         <v>24</v>
       </c>
-      <c r="C71">
+      <c r="D71">
         <v>58</v>
       </c>
-      <c r="D71">
+      <c r="E71">
         <v>674</v>
       </c>
-      <c r="E71">
+      <c r="F71">
         <v>831</v>
       </c>
-      <c r="F71">
+      <c r="G71">
         <v>832</v>
       </c>
-      <c r="G71">
+      <c r="H71">
         <v>1234</v>
       </c>
-      <c r="H71">
+      <c r="I71">
         <v>1303</v>
       </c>
-      <c r="I71">
+      <c r="J71">
         <v>1446</v>
       </c>
-      <c r="J71">
+      <c r="K71">
         <v>1634</v>
       </c>
-      <c r="K71">
+      <c r="L71">
         <v>1698</v>
       </c>
-      <c r="L71">
+      <c r="M71">
         <v>1837</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72">
         <v>359</v>
       </c>
-      <c r="B72">
+      <c r="C72">
         <v>495</v>
       </c>
-      <c r="C72">
+      <c r="D72">
         <v>548</v>
       </c>
-      <c r="D72">
+      <c r="E72">
         <v>658</v>
       </c>
-      <c r="E72">
+      <c r="F72">
         <v>746</v>
       </c>
-      <c r="F72">
+      <c r="G72">
         <v>1315</v>
       </c>
-      <c r="G72">
+      <c r="H72">
         <v>1449</v>
       </c>
-      <c r="H72">
+      <c r="I72">
         <v>1457</v>
       </c>
-      <c r="I72">
+      <c r="J72">
         <v>1458</v>
       </c>
-      <c r="J72">
+      <c r="K72">
         <v>1646</v>
       </c>
-      <c r="K72">
+      <c r="L72">
         <v>1649</v>
       </c>
-      <c r="L72">
+      <c r="M72">
         <v>2028</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73">
         <v>77</v>
       </c>
-      <c r="B73">
+      <c r="C73">
         <v>78</v>
       </c>
-      <c r="C73">
+      <c r="D73">
         <v>79</v>
       </c>
-      <c r="D73">
+      <c r="E73">
         <v>116</v>
       </c>
-      <c r="E73">
+      <c r="F73">
         <v>262</v>
       </c>
-      <c r="F73">
+      <c r="G73">
         <v>643</v>
       </c>
-      <c r="G73">
+      <c r="H73">
         <v>669</v>
       </c>
-      <c r="H73">
+      <c r="I73">
         <v>995</v>
       </c>
-      <c r="I73">
+      <c r="J73">
         <v>1107</v>
       </c>
-      <c r="J73">
+      <c r="K73">
         <v>1418</v>
       </c>
-      <c r="K73">
+      <c r="L73">
         <v>1969</v>
       </c>
-      <c r="L73">
+      <c r="M73">
         <v>2047</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74">
         <v>256</v>
       </c>
-      <c r="B74">
+      <c r="C74">
         <v>328</v>
       </c>
-      <c r="C74">
+      <c r="D74">
         <v>741</v>
       </c>
-      <c r="D74">
+      <c r="E74">
         <v>1137</v>
       </c>
-      <c r="E74">
+      <c r="F74">
         <v>1388</v>
       </c>
-      <c r="F74">
+      <c r="G74">
         <v>1406</v>
       </c>
-      <c r="G74">
+      <c r="H74">
         <v>1504</v>
       </c>
-      <c r="H74">
+      <c r="I74">
         <v>1620</v>
       </c>
-      <c r="I74">
+      <c r="J74">
         <v>1627</v>
       </c>
-      <c r="J74">
+      <c r="K74">
         <v>1630</v>
       </c>
-      <c r="K74">
+      <c r="L74">
         <v>2030</v>
       </c>
-      <c r="L74">
+      <c r="M74">
         <v>2031</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75">
         <v>82</v>
       </c>
-      <c r="B75">
+      <c r="C75">
         <v>113</v>
       </c>
-      <c r="C75">
+      <c r="D75">
         <v>257</v>
       </c>
-      <c r="D75">
+      <c r="E75">
         <v>278</v>
       </c>
-      <c r="E75">
+      <c r="F75">
         <v>445</v>
       </c>
-      <c r="F75">
+      <c r="G75">
         <v>786</v>
       </c>
-      <c r="G75">
+      <c r="H75">
         <v>1039</v>
       </c>
-      <c r="H75">
+      <c r="I75">
         <v>1392</v>
       </c>
-      <c r="I75">
+      <c r="J75">
         <v>1473</v>
       </c>
-      <c r="J75">
+      <c r="K75">
         <v>1782</v>
       </c>
-      <c r="K75">
+      <c r="L75">
         <v>1859</v>
       </c>
-      <c r="L75">
+      <c r="M75">
         <v>1997</v>
       </c>
-      <c r="M75">
+      <c r="N75">
         <v>2040</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76">
         <v>130</v>
       </c>
-      <c r="B76">
+      <c r="C76">
         <v>235</v>
       </c>
-      <c r="C76">
+      <c r="D76">
         <v>320</v>
       </c>
-      <c r="D76">
+      <c r="E76">
         <v>433</v>
       </c>
-      <c r="E76">
+      <c r="F76">
         <v>620</v>
       </c>
-      <c r="F76">
+      <c r="G76">
         <v>769</v>
       </c>
-      <c r="G76">
+      <c r="H76">
         <v>849</v>
       </c>
-      <c r="H76">
+      <c r="I76">
         <v>952</v>
       </c>
-      <c r="I76">
+      <c r="J76">
         <v>1221</v>
       </c>
-      <c r="J76">
+      <c r="K76">
         <v>1689</v>
       </c>
-      <c r="K76">
+      <c r="L76">
         <v>1712</v>
       </c>
-      <c r="L76">
+      <c r="M76">
         <v>2051</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77">
         <v>189</v>
       </c>
-      <c r="B77">
+      <c r="C77">
         <v>195</v>
       </c>
-      <c r="C77">
+      <c r="D77">
         <v>198</v>
       </c>
-      <c r="D77">
+      <c r="E77">
         <v>388</v>
       </c>
-      <c r="E77">
+      <c r="F77">
         <v>575</v>
       </c>
-      <c r="F77">
+      <c r="G77">
         <v>945</v>
       </c>
-      <c r="G77">
+      <c r="H77">
         <v>958</v>
       </c>
-      <c r="H77">
+      <c r="I77">
         <v>1078</v>
       </c>
-      <c r="I77">
+      <c r="J77">
         <v>1297</v>
       </c>
-      <c r="J77">
+      <c r="K77">
         <v>1541</v>
       </c>
-      <c r="K77">
+      <c r="L77">
         <v>1591</v>
       </c>
-      <c r="L77">
+      <c r="M77">
         <v>1726</v>
       </c>
-      <c r="M77">
+      <c r="N77">
         <v>2024</v>
       </c>
-      <c r="N77">
+      <c r="O77">
         <v>2067</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78">
         <v>212</v>
       </c>
-      <c r="B78">
+      <c r="C78">
         <v>617</v>
       </c>
-      <c r="C78">
+      <c r="D78">
         <v>631</v>
       </c>
-      <c r="D78">
+      <c r="E78">
         <v>697</v>
       </c>
-      <c r="E78">
+      <c r="F78">
         <v>916</v>
       </c>
-      <c r="F78">
+      <c r="G78">
         <v>919</v>
       </c>
-      <c r="G78">
+      <c r="H78">
         <v>927</v>
       </c>
-      <c r="H78">
+      <c r="I78">
         <v>954</v>
       </c>
-      <c r="I78">
+      <c r="J78">
         <v>1079</v>
       </c>
-      <c r="J78">
+      <c r="K78">
         <v>1081</v>
       </c>
-      <c r="K78">
+      <c r="L78">
         <v>1524</v>
       </c>
-      <c r="L78">
+      <c r="M78">
         <v>1643</v>
       </c>
-      <c r="M78">
+      <c r="N78">
         <v>1923</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79">
         <v>199</v>
       </c>
-      <c r="B79">
+      <c r="C79">
         <v>604</v>
       </c>
-      <c r="C79">
+      <c r="D79">
         <v>637</v>
       </c>
-      <c r="D79">
+      <c r="E79">
         <v>640</v>
       </c>
-      <c r="E79">
+      <c r="F79">
         <v>896</v>
       </c>
-      <c r="F79">
+      <c r="G79">
         <v>1300</v>
       </c>
-      <c r="G79">
+      <c r="H79">
         <v>1301</v>
       </c>
-      <c r="H79">
+      <c r="I79">
         <v>1396</v>
       </c>
-      <c r="I79">
+      <c r="J79">
         <v>1593</v>
       </c>
-      <c r="J79">
+      <c r="K79">
         <v>2013</v>
       </c>
-      <c r="K79">
+      <c r="L79">
         <v>2094</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80">
         <v>123</v>
       </c>
-      <c r="B80">
+      <c r="C80">
         <v>224</v>
       </c>
-      <c r="C80">
+      <c r="D80">
         <v>304</v>
       </c>
-      <c r="D80">
+      <c r="E80">
         <v>562</v>
       </c>
-      <c r="E80">
+      <c r="F80">
         <v>563</v>
       </c>
-      <c r="F80">
+      <c r="G80">
         <v>565</v>
       </c>
-      <c r="G80">
+      <c r="H80">
         <v>600</v>
       </c>
-      <c r="H80">
+      <c r="I80">
         <v>607</v>
       </c>
-      <c r="I80">
+      <c r="J80">
         <v>1045</v>
       </c>
-      <c r="J80">
+      <c r="K80">
         <v>1426</v>
       </c>
-      <c r="K80">
+      <c r="L80">
         <v>1583</v>
       </c>
-      <c r="L80">
+      <c r="M80">
         <v>1599</v>
       </c>
-      <c r="M80">
+      <c r="N80">
         <v>1659</v>
       </c>
-      <c r="N80">
+      <c r="O80">
         <v>2099</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81">
         <v>115</v>
       </c>
-      <c r="B81">
+      <c r="C81">
         <v>126</v>
       </c>
-      <c r="C81">
+      <c r="D81">
         <v>409</v>
       </c>
-      <c r="D81">
+      <c r="E81">
         <v>553</v>
       </c>
-      <c r="E81">
+      <c r="F81">
         <v>673</v>
       </c>
-      <c r="F81">
+      <c r="G81">
         <v>704</v>
       </c>
-      <c r="G81">
+      <c r="H81">
         <v>706</v>
       </c>
-      <c r="H81">
+      <c r="I81">
         <v>1390</v>
       </c>
-      <c r="I81">
+      <c r="J81">
         <v>1637</v>
       </c>
-      <c r="J81">
+      <c r="K81">
         <v>1662</v>
       </c>
-      <c r="K81">
+      <c r="L81">
         <v>1959</v>
       </c>
-      <c r="L81">
+      <c r="M81">
         <v>2065</v>
       </c>
-      <c r="M81">
+      <c r="N81">
         <v>2066</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82">
         <v>193</v>
       </c>
-      <c r="B82">
+      <c r="C82">
         <v>197</v>
       </c>
-      <c r="C82">
+      <c r="D82">
         <v>207</v>
       </c>
-      <c r="D82">
+      <c r="E82">
         <v>499</v>
       </c>
-      <c r="E82">
+      <c r="F82">
         <v>570</v>
       </c>
-      <c r="F82">
+      <c r="G82">
         <v>960</v>
       </c>
-      <c r="G82">
+      <c r="H82">
         <v>1016</v>
       </c>
-      <c r="H82">
+      <c r="I82">
         <v>1048</v>
       </c>
-      <c r="I82">
+      <c r="J82">
         <v>1058</v>
       </c>
-      <c r="J82">
+      <c r="K82">
         <v>1085</v>
       </c>
-      <c r="K82">
+      <c r="L82">
         <v>1183</v>
       </c>
-      <c r="L82">
+      <c r="M82">
         <v>1212</v>
       </c>
-      <c r="M82">
+      <c r="N82">
         <v>1501</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83">
         <v>1244</v>
       </c>
-      <c r="B83">
+      <c r="C83">
         <v>1294</v>
       </c>
-      <c r="C83">
+      <c r="D83">
         <v>1476</v>
       </c>
-      <c r="D83">
+      <c r="E83">
         <v>1478</v>
       </c>
-      <c r="E83">
+      <c r="F83">
         <v>1481</v>
       </c>
-      <c r="F83">
+      <c r="G83">
         <v>1608</v>
       </c>
-      <c r="G83">
+      <c r="H83">
         <v>1668</v>
       </c>
-      <c r="H83">
+      <c r="I83">
         <v>1671</v>
       </c>
-      <c r="I83">
+      <c r="J83">
         <v>1672</v>
       </c>
-      <c r="J83">
+      <c r="K83">
         <v>1673</v>
       </c>
-      <c r="K83">
+      <c r="L83">
         <v>1674</v>
       </c>
-      <c r="L83">
+      <c r="M83">
         <v>1675</v>
       </c>
-      <c r="M83">
+      <c r="N83">
         <v>1677</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84">
         <v>392</v>
       </c>
-      <c r="B84">
+      <c r="C84">
         <v>625</v>
       </c>
-      <c r="C84">
+      <c r="D84">
         <v>698</v>
       </c>
-      <c r="D84">
+      <c r="E84">
         <v>846</v>
       </c>
-      <c r="E84">
+      <c r="F84">
         <v>873</v>
       </c>
-      <c r="F84">
+      <c r="G84">
         <v>1077</v>
       </c>
-      <c r="G84">
+      <c r="H84">
         <v>1295</v>
       </c>
-      <c r="H84">
+      <c r="I84">
         <v>1733</v>
       </c>
-      <c r="I84">
+      <c r="J84">
         <v>1805</v>
       </c>
-      <c r="J84">
+      <c r="K84">
         <v>1822</v>
       </c>
-      <c r="K84">
+      <c r="L84">
         <v>2078</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85">
         <v>789</v>
       </c>
-      <c r="B85">
+      <c r="C85">
         <v>921</v>
       </c>
-      <c r="C85">
+      <c r="D85">
         <v>1148</v>
       </c>
-      <c r="D85">
+      <c r="E85">
         <v>1161</v>
       </c>
-      <c r="E85">
+      <c r="F85">
         <v>1381</v>
       </c>
-      <c r="F85">
+      <c r="G85">
         <v>1383</v>
       </c>
-      <c r="G85">
+      <c r="H85">
         <v>1454</v>
       </c>
-      <c r="H85">
+      <c r="I85">
         <v>1595</v>
       </c>
-      <c r="I85">
+      <c r="J85">
         <v>1693</v>
       </c>
-      <c r="J85">
+      <c r="K85">
         <v>1866</v>
       </c>
-      <c r="K85">
+      <c r="L85">
         <v>1869</v>
       </c>
-      <c r="L85">
+      <c r="M85">
         <v>1879</v>
       </c>
-      <c r="M85">
+      <c r="N85">
         <v>1981</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86">
         <v>5</v>
       </c>
-      <c r="B86">
+      <c r="C86">
         <v>297</v>
       </c>
-      <c r="C86">
+      <c r="D86">
         <v>305</v>
       </c>
-      <c r="D86">
+      <c r="E86">
         <v>329</v>
       </c>
-      <c r="E86">
+      <c r="F86">
         <v>511</v>
       </c>
-      <c r="F86">
+      <c r="G86">
         <v>537</v>
       </c>
-      <c r="G86">
+      <c r="H86">
         <v>590</v>
       </c>
-      <c r="H86">
+      <c r="I86">
         <v>591</v>
       </c>
-      <c r="I86">
+      <c r="J86">
         <v>1173</v>
       </c>
-      <c r="J86">
+      <c r="K86">
         <v>1403</v>
       </c>
-      <c r="K86">
+      <c r="L86">
         <v>1453</v>
       </c>
-      <c r="L86">
+      <c r="M86">
         <v>1685</v>
       </c>
-      <c r="M86">
+      <c r="N86">
         <v>1777</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87">
         <v>312</v>
       </c>
-      <c r="B87">
+      <c r="C87">
         <v>389</v>
       </c>
-      <c r="C87">
+      <c r="D87">
         <v>453</v>
       </c>
-      <c r="D87">
+      <c r="E87">
         <v>781</v>
       </c>
-      <c r="E87">
+      <c r="F87">
         <v>1099</v>
       </c>
-      <c r="F87">
+      <c r="G87">
         <v>1144</v>
       </c>
-      <c r="G87">
+      <c r="H87">
         <v>1185</v>
       </c>
-      <c r="H87">
+      <c r="I87">
         <v>1431</v>
       </c>
-      <c r="I87">
+      <c r="J87">
         <v>1452</v>
       </c>
-      <c r="J87">
+      <c r="K87">
         <v>1770</v>
       </c>
-      <c r="K87">
+      <c r="L87">
         <v>1826</v>
       </c>
-      <c r="L87">
+      <c r="M87">
         <v>1840</v>
       </c>
-      <c r="M87">
+      <c r="N87">
         <v>1860</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88">
         <v>54</v>
       </c>
-      <c r="B88">
+      <c r="C88">
         <v>177</v>
       </c>
-      <c r="C88">
+      <c r="D88">
         <v>310</v>
       </c>
-      <c r="D88">
+      <c r="E88">
         <v>935</v>
       </c>
-      <c r="E88">
+      <c r="F88">
         <v>1002</v>
       </c>
-      <c r="F88">
+      <c r="G88">
         <v>1025</v>
       </c>
-      <c r="G88">
+      <c r="H88">
         <v>1074</v>
       </c>
-      <c r="H88">
+      <c r="I88">
         <v>1167</v>
       </c>
-      <c r="I88">
+      <c r="J88">
         <v>1335</v>
       </c>
-      <c r="J88">
+      <c r="K88">
         <v>1749</v>
       </c>
-      <c r="K88">
+      <c r="L88">
         <v>1846</v>
       </c>
-      <c r="L88">
+      <c r="M88">
         <v>1897</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89">
         <v>211</v>
       </c>
-      <c r="B89">
+      <c r="C89">
         <v>571</v>
       </c>
-      <c r="C89">
+      <c r="D89">
         <v>668</v>
       </c>
-      <c r="D89">
+      <c r="E89">
         <v>738</v>
       </c>
-      <c r="E89">
+      <c r="F89">
         <v>1130</v>
       </c>
-      <c r="F89">
+      <c r="G89">
         <v>1282</v>
       </c>
-      <c r="G89">
+      <c r="H89">
         <v>1323</v>
       </c>
-      <c r="H89">
+      <c r="I89">
         <v>1362</v>
       </c>
-      <c r="I89">
+      <c r="J89">
         <v>1364</v>
       </c>
-      <c r="J89">
+      <c r="K89">
         <v>1447</v>
       </c>
-      <c r="K89">
+      <c r="L89">
         <v>1619</v>
       </c>
-      <c r="L89">
+      <c r="M89">
         <v>2063</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90">
         <v>81</v>
       </c>
-      <c r="B90">
+      <c r="C90">
         <v>375</v>
       </c>
-      <c r="C90">
+      <c r="D90">
         <v>443</v>
       </c>
-      <c r="D90">
+      <c r="E90">
         <v>865</v>
       </c>
-      <c r="E90">
+      <c r="F90">
         <v>983</v>
       </c>
-      <c r="F90">
+      <c r="G90">
         <v>997</v>
       </c>
-      <c r="G90">
+      <c r="H90">
         <v>1236</v>
       </c>
-      <c r="H90">
+      <c r="I90">
         <v>1307</v>
       </c>
-      <c r="I90">
+      <c r="J90">
         <v>1448</v>
       </c>
-      <c r="J90">
+      <c r="K90">
         <v>1629</v>
       </c>
-      <c r="K90">
+      <c r="L90">
         <v>1787</v>
       </c>
-      <c r="L90">
+      <c r="M90">
         <v>1956</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91">
         <v>31</v>
       </c>
-      <c r="B91">
+      <c r="C91">
         <v>141</v>
       </c>
-      <c r="C91">
+      <c r="D91">
         <v>279</v>
       </c>
-      <c r="D91">
+      <c r="E91">
         <v>298</v>
       </c>
-      <c r="E91">
+      <c r="F91">
         <v>476</v>
       </c>
-      <c r="F91">
+      <c r="G91">
         <v>481</v>
       </c>
-      <c r="G91">
+      <c r="H91">
         <v>703</v>
       </c>
-      <c r="H91">
+      <c r="I91">
         <v>1003</v>
       </c>
-      <c r="I91">
+      <c r="J91">
         <v>1126</v>
       </c>
-      <c r="J91">
+      <c r="K91">
         <v>1197</v>
       </c>
-      <c r="K91">
+      <c r="L91">
         <v>1628</v>
       </c>
-      <c r="L91">
+      <c r="M91">
         <v>1824</v>
       </c>
-      <c r="M91">
+      <c r="N91">
         <v>1863</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92">
         <v>39</v>
       </c>
-      <c r="B92">
+      <c r="C92">
         <v>95</v>
       </c>
-      <c r="C92">
+      <c r="D92">
         <v>96</v>
       </c>
-      <c r="D92">
+      <c r="E92">
         <v>99</v>
       </c>
-      <c r="E92">
+      <c r="F92">
         <v>114</v>
       </c>
-      <c r="F92">
+      <c r="G92">
         <v>142</v>
       </c>
-      <c r="G92">
+      <c r="H92">
         <v>367</v>
       </c>
-      <c r="H92">
+      <c r="I92">
         <v>451</v>
       </c>
-      <c r="I92">
+      <c r="J92">
         <v>728</v>
       </c>
-      <c r="J92">
+      <c r="K92">
         <v>1068</v>
       </c>
-      <c r="K92">
+      <c r="L92">
         <v>1485</v>
       </c>
-      <c r="L92">
+      <c r="M92">
         <v>1823</v>
       </c>
-      <c r="M92">
+      <c r="N92">
         <v>2011</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93">
         <v>628</v>
       </c>
-      <c r="B93">
+      <c r="C93">
         <v>726</v>
       </c>
-      <c r="C93">
+      <c r="D93">
         <v>1498</v>
       </c>
-      <c r="D93">
+      <c r="E93">
         <v>1502</v>
       </c>
-      <c r="E93">
+      <c r="F93">
         <v>1642</v>
       </c>
-      <c r="F93">
+      <c r="G93">
         <v>1757</v>
       </c>
-      <c r="G93">
+      <c r="H93">
         <v>1764</v>
       </c>
-      <c r="H93">
+      <c r="I93">
         <v>1813</v>
       </c>
-      <c r="I93">
+      <c r="J93">
         <v>1884</v>
       </c>
-      <c r="J93">
+      <c r="K93">
         <v>1960</v>
       </c>
-      <c r="K93">
+      <c r="L93">
         <v>2001</v>
       </c>
-      <c r="L93">
+      <c r="M93">
         <v>2002</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94">
         <v>220</v>
       </c>
-      <c r="B94">
+      <c r="C94">
         <v>420</v>
       </c>
-      <c r="C94">
+      <c r="D94">
         <v>1209</v>
       </c>
-      <c r="D94">
+      <c r="E94">
         <v>1210</v>
       </c>
-      <c r="E94">
+      <c r="F94">
         <v>1214</v>
       </c>
-      <c r="F94">
+      <c r="G94">
         <v>1354</v>
       </c>
-      <c r="G94">
+      <c r="H94">
         <v>1477</v>
       </c>
-      <c r="H94">
+      <c r="I94">
         <v>1613</v>
       </c>
-      <c r="I94">
+      <c r="J94">
         <v>1701</v>
       </c>
-      <c r="J94">
+      <c r="K94">
         <v>1702</v>
       </c>
-      <c r="K94">
+      <c r="L94">
         <v>1905</v>
       </c>
-      <c r="L94">
+      <c r="M94">
         <v>1906</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95">
         <v>192</v>
       </c>
-      <c r="B95">
+      <c r="C95">
         <v>601</v>
       </c>
-      <c r="C95">
+      <c r="D95">
         <v>605</v>
       </c>
-      <c r="D95">
+      <c r="E95">
         <v>622</v>
       </c>
-      <c r="E95">
+      <c r="F95">
         <v>1355</v>
       </c>
-      <c r="F95">
+      <c r="G95">
         <v>1464</v>
       </c>
-      <c r="G95">
+      <c r="H95">
         <v>1480</v>
       </c>
-      <c r="H95">
+      <c r="I95">
         <v>1670</v>
       </c>
-      <c r="I95">
+      <c r="J95">
         <v>1678</v>
       </c>
-      <c r="J95">
+      <c r="K95">
         <v>1686</v>
       </c>
-      <c r="K95">
+      <c r="L95">
         <v>1896</v>
       </c>
-      <c r="L95">
+      <c r="M95">
         <v>2036</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96">
         <v>293</v>
       </c>
-      <c r="B96">
+      <c r="C96">
         <v>588</v>
       </c>
-      <c r="C96">
+      <c r="D96">
         <v>612</v>
       </c>
-      <c r="D96">
+      <c r="E96">
         <v>892</v>
       </c>
-      <c r="E96">
+      <c r="F96">
         <v>1069</v>
       </c>
-      <c r="F96">
+      <c r="G96">
         <v>1133</v>
       </c>
-      <c r="G96">
+      <c r="H96">
         <v>1538</v>
       </c>
-      <c r="H96">
+      <c r="I96">
         <v>1667</v>
       </c>
-      <c r="I96">
+      <c r="J96">
         <v>1669</v>
       </c>
-      <c r="J96">
+      <c r="K96">
         <v>1676</v>
       </c>
-      <c r="K96">
+      <c r="L96">
         <v>1679</v>
       </c>
-      <c r="L96">
+      <c r="M96">
         <v>1861</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97">
         <v>187</v>
       </c>
-      <c r="B97">
+      <c r="C97">
         <v>260</v>
       </c>
-      <c r="C97">
+      <c r="D97">
         <v>319</v>
       </c>
-      <c r="D97">
+      <c r="E97">
         <v>525</v>
       </c>
-      <c r="E97">
+      <c r="F97">
         <v>547</v>
       </c>
-      <c r="F97">
+      <c r="G97">
         <v>862</v>
       </c>
-      <c r="G97">
+      <c r="H97">
         <v>939</v>
       </c>
-      <c r="H97">
+      <c r="I97">
         <v>1034</v>
       </c>
-      <c r="I97">
+      <c r="J97">
         <v>1098</v>
       </c>
-      <c r="J97">
+      <c r="K97">
         <v>1369</v>
       </c>
-      <c r="K97">
+      <c r="L97">
         <v>1442</v>
       </c>
-      <c r="L97">
+      <c r="M97">
         <v>1704</v>
       </c>
-      <c r="M97">
+      <c r="N97">
         <v>2103</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98">
         <v>181</v>
       </c>
-      <c r="B98">
+      <c r="C98">
         <v>226</v>
       </c>
-      <c r="C98">
+      <c r="D98">
         <v>368</v>
       </c>
-      <c r="D98">
+      <c r="E98">
         <v>397</v>
       </c>
-      <c r="E98">
+      <c r="F98">
         <v>500</v>
       </c>
-      <c r="F98">
+      <c r="G98">
         <v>582</v>
       </c>
-      <c r="G98">
+      <c r="H98">
         <v>842</v>
       </c>
-      <c r="H98">
+      <c r="I98">
         <v>944</v>
       </c>
-      <c r="I98">
+      <c r="J98">
         <v>1288</v>
       </c>
-      <c r="J98">
+      <c r="K98">
         <v>1587</v>
       </c>
-      <c r="K98">
+      <c r="L98">
         <v>1920</v>
       </c>
-      <c r="L98">
+      <c r="M98">
         <v>1955</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99">
         <v>93</v>
       </c>
-      <c r="B99">
+      <c r="C99">
         <v>97</v>
       </c>
-      <c r="C99">
+      <c r="D99">
         <v>731</v>
       </c>
-      <c r="D99">
+      <c r="E99">
         <v>747</v>
       </c>
-      <c r="E99">
+      <c r="F99">
         <v>858</v>
       </c>
-      <c r="F99">
+      <c r="G99">
         <v>937</v>
       </c>
-      <c r="G99">
+      <c r="H99">
         <v>1136</v>
       </c>
-      <c r="H99">
+      <c r="I99">
         <v>1179</v>
       </c>
-      <c r="I99">
+      <c r="J99">
         <v>1505</v>
       </c>
-      <c r="J99">
+      <c r="K99">
         <v>1680</v>
       </c>
-      <c r="K99">
+      <c r="L99">
         <v>1746</v>
       </c>
-      <c r="L99">
+      <c r="M99">
         <v>2048</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100">
         <v>29</v>
       </c>
-      <c r="B100">
+      <c r="C100">
         <v>55</v>
       </c>
-      <c r="C100">
+      <c r="D100">
         <v>253</v>
       </c>
-      <c r="D100">
+      <c r="E100">
         <v>292</v>
       </c>
-      <c r="E100">
+      <c r="F100">
         <v>522</v>
       </c>
-      <c r="F100">
+      <c r="G100">
         <v>645</v>
       </c>
-      <c r="G100">
+      <c r="H100">
         <v>727</v>
       </c>
-      <c r="H100">
+      <c r="I100">
         <v>1177</v>
       </c>
-      <c r="I100">
+      <c r="J100">
         <v>1178</v>
       </c>
-      <c r="J100">
+      <c r="K100">
         <v>1192</v>
       </c>
-      <c r="K100">
+      <c r="L100">
         <v>1456</v>
       </c>
-      <c r="L100">
+      <c r="M100">
         <v>1951</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101">
         <v>92</v>
       </c>
-      <c r="B101">
+      <c r="C101">
         <v>101</v>
       </c>
-      <c r="C101">
+      <c r="D101">
         <v>102</v>
       </c>
-      <c r="D101">
+      <c r="E101">
         <v>526</v>
       </c>
-      <c r="E101">
+      <c r="F101">
         <v>724</v>
       </c>
-      <c r="F101">
+      <c r="G101">
         <v>888</v>
       </c>
-      <c r="G101">
+      <c r="H101">
         <v>890</v>
       </c>
-      <c r="H101">
+      <c r="I101">
         <v>891</v>
       </c>
-      <c r="I101">
+      <c r="J101">
         <v>1318</v>
       </c>
-      <c r="J101">
+      <c r="K101">
         <v>1451</v>
       </c>
-      <c r="K101">
+      <c r="L101">
         <v>1725</v>
       </c>
-      <c r="L101">
+      <c r="M101">
         <v>1727</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102">
         <v>317</v>
       </c>
-      <c r="B102">
+      <c r="C102">
         <v>583</v>
       </c>
-      <c r="C102">
+      <c r="D102">
         <v>632</v>
       </c>
-      <c r="D102">
+      <c r="E102">
         <v>898</v>
       </c>
-      <c r="E102">
+      <c r="F102">
         <v>1114</v>
       </c>
-      <c r="F102">
+      <c r="G102">
         <v>1267</v>
       </c>
-      <c r="G102">
+      <c r="H102">
         <v>1278</v>
       </c>
-      <c r="H102">
+      <c r="I102">
         <v>1363</v>
       </c>
-      <c r="I102">
+      <c r="J102">
         <v>1372</v>
       </c>
-      <c r="J102">
+      <c r="K102">
         <v>1580</v>
       </c>
-      <c r="K102">
+      <c r="L102">
         <v>1615</v>
       </c>
-      <c r="L102">
+      <c r="M102">
         <v>1802</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103">
         <v>287</v>
       </c>
-      <c r="B103">
+      <c r="C103">
         <v>535</v>
       </c>
-      <c r="C103">
+      <c r="D103">
         <v>744</v>
       </c>
-      <c r="D103">
+      <c r="E103">
         <v>745</v>
       </c>
-      <c r="E103">
+      <c r="F103">
         <v>1032</v>
       </c>
-      <c r="F103">
+      <c r="G103">
         <v>1162</v>
       </c>
-      <c r="G103">
+      <c r="H103">
         <v>1325</v>
       </c>
-      <c r="H103">
+      <c r="I103">
         <v>1912</v>
       </c>
-      <c r="I103">
+      <c r="J103">
         <v>1965</v>
       </c>
-      <c r="J103">
+      <c r="K103">
         <v>1967</v>
       </c>
-      <c r="K103">
+      <c r="L103">
         <v>2005</v>
       </c>
-      <c r="L103">
+      <c r="M103">
         <v>2006</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104">
         <v>516</v>
       </c>
-      <c r="B104">
+      <c r="C104">
         <v>1070</v>
       </c>
-      <c r="C104">
+      <c r="D104">
         <v>1284</v>
       </c>
-      <c r="D104">
+      <c r="E104">
         <v>1313</v>
       </c>
-      <c r="E104">
+      <c r="F104">
         <v>1314</v>
       </c>
-      <c r="F104">
+      <c r="G104">
         <v>1319</v>
       </c>
-      <c r="G104">
+      <c r="H104">
         <v>1697</v>
       </c>
-      <c r="H104">
+      <c r="I104">
         <v>1714</v>
       </c>
-      <c r="I104">
+      <c r="J104">
         <v>1754</v>
       </c>
-      <c r="J104">
+      <c r="K104">
         <v>1929</v>
       </c>
-      <c r="K104">
+      <c r="L104">
         <v>2044</v>
       </c>
-      <c r="L104">
+      <c r="M104">
         <v>2046</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105">
         <v>330</v>
       </c>
-      <c r="B105">
+      <c r="C105">
         <v>348</v>
       </c>
-      <c r="C105">
+      <c r="D105">
         <v>352</v>
       </c>
-      <c r="D105">
+      <c r="E105">
         <v>370</v>
       </c>
-      <c r="E105">
+      <c r="F105">
         <v>649</v>
       </c>
-      <c r="F105">
+      <c r="G105">
         <v>650</v>
       </c>
-      <c r="G105">
+      <c r="H105">
         <v>949</v>
       </c>
-      <c r="H105">
+      <c r="I105">
         <v>1285</v>
       </c>
-      <c r="I105">
+      <c r="J105">
         <v>1820</v>
       </c>
-      <c r="J105">
+      <c r="K105">
         <v>1917</v>
       </c>
-      <c r="K105">
+      <c r="L105">
         <v>2101</v>
       </c>
-      <c r="L105">
+      <c r="M105">
         <v>2102</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106">
         <v>12</v>
       </c>
-      <c r="B106">
+      <c r="C106">
         <v>15</v>
       </c>
-      <c r="C106">
+      <c r="D106">
         <v>885</v>
       </c>
-      <c r="D106">
+      <c r="E106">
         <v>973</v>
       </c>
-      <c r="E106">
+      <c r="F106">
         <v>1120</v>
       </c>
-      <c r="F106">
+      <c r="G106">
         <v>1135</v>
       </c>
-      <c r="G106">
+      <c r="H106">
         <v>1146</v>
       </c>
-      <c r="H106">
+      <c r="I106">
         <v>1241</v>
       </c>
-      <c r="I106">
+      <c r="J106">
         <v>1274</v>
       </c>
-      <c r="J106">
+      <c r="K106">
         <v>1385</v>
       </c>
-      <c r="K106">
+      <c r="L106">
         <v>1899</v>
       </c>
-      <c r="L106">
+      <c r="M106">
         <v>1935</v>
       </c>
-      <c r="M106">
+      <c r="N106">
         <v>2105</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107">
         <v>13</v>
       </c>
-      <c r="B107">
+      <c r="C107">
         <v>732</v>
       </c>
-      <c r="C107">
+      <c r="D107">
         <v>970</v>
       </c>
-      <c r="D107">
+      <c r="E107">
         <v>971</v>
       </c>
-      <c r="E107">
+      <c r="F107">
         <v>1011</v>
       </c>
-      <c r="F107">
+      <c r="G107">
         <v>1013</v>
       </c>
-      <c r="G107">
+      <c r="H107">
         <v>1014</v>
       </c>
-      <c r="H107">
+      <c r="I107">
         <v>1169</v>
       </c>
-      <c r="I107">
+      <c r="J107">
         <v>1226</v>
       </c>
-      <c r="J107">
+      <c r="K107">
         <v>1466</v>
       </c>
-      <c r="K107">
+      <c r="L107">
         <v>1648</v>
       </c>
-      <c r="L107">
+      <c r="M107">
         <v>1847</v>
       </c>
-      <c r="M107">
+      <c r="N107">
         <v>2056</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108">
         <v>45</v>
       </c>
-      <c r="B108">
+      <c r="C108">
         <v>47</v>
       </c>
-      <c r="C108">
+      <c r="D108">
         <v>48</v>
       </c>
-      <c r="D108">
+      <c r="E108">
         <v>49</v>
       </c>
-      <c r="E108">
+      <c r="F108">
         <v>166</v>
       </c>
-      <c r="F108">
+      <c r="G108">
         <v>449</v>
       </c>
-      <c r="G108">
+      <c r="H108">
         <v>488</v>
       </c>
-      <c r="H108">
+      <c r="I108">
         <v>780</v>
       </c>
-      <c r="I108">
+      <c r="J108">
         <v>799</v>
       </c>
-      <c r="J108">
+      <c r="K108">
         <v>819</v>
       </c>
-      <c r="K108">
+      <c r="L108">
         <v>1261</v>
       </c>
-      <c r="L108">
+      <c r="M108">
         <v>1500</v>
       </c>
-      <c r="M108">
+      <c r="N108">
         <v>2025</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109">
         <v>18</v>
       </c>
-      <c r="B109">
+      <c r="C109">
         <v>336</v>
       </c>
-      <c r="C109">
+      <c r="D109">
         <v>337</v>
       </c>
-      <c r="D109">
+      <c r="E109">
         <v>466</v>
       </c>
-      <c r="E109">
+      <c r="F109">
         <v>757</v>
       </c>
-      <c r="F109">
+      <c r="G109">
         <v>901</v>
       </c>
-      <c r="G109">
+      <c r="H109">
         <v>1010</v>
       </c>
-      <c r="H109">
+      <c r="I109">
         <v>1139</v>
       </c>
-      <c r="I109">
+      <c r="J109">
         <v>1389</v>
       </c>
-      <c r="J109">
+      <c r="K109">
         <v>1409</v>
       </c>
-      <c r="K109">
+      <c r="L109">
         <v>1441</v>
       </c>
-      <c r="L109">
+      <c r="M109">
         <v>1827</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>109</v>
       </c>
       <c r="B110">
+        <v>109</v>
+      </c>
+      <c r="C110">
         <v>133</v>
       </c>
-      <c r="C110">
+      <c r="D110">
         <v>442</v>
       </c>
-      <c r="D110">
+      <c r="E110">
         <v>514</v>
       </c>
-      <c r="E110">
+      <c r="F110">
         <v>560</v>
       </c>
-      <c r="F110">
+      <c r="G110">
         <v>609</v>
       </c>
-      <c r="G110">
+      <c r="H110">
         <v>861</v>
       </c>
-      <c r="H110">
+      <c r="I110">
         <v>894</v>
       </c>
-      <c r="I110">
+      <c r="J110">
         <v>1055</v>
       </c>
-      <c r="J110">
+      <c r="K110">
         <v>1071</v>
       </c>
-      <c r="K110">
+      <c r="L110">
         <v>1075</v>
       </c>
-      <c r="L110">
+      <c r="M110">
         <v>1427</v>
       </c>
-      <c r="M110">
+      <c r="N110">
         <v>1545</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111">
         <v>121</v>
       </c>
-      <c r="B111">
+      <c r="C111">
         <v>167</v>
       </c>
-      <c r="C111">
+      <c r="D111">
         <v>639</v>
       </c>
-      <c r="D111">
+      <c r="E111">
         <v>1324</v>
       </c>
-      <c r="E111">
+      <c r="F111">
         <v>1337</v>
       </c>
-      <c r="F111">
+      <c r="G111">
         <v>1386</v>
       </c>
-      <c r="G111">
+      <c r="H111">
         <v>1429</v>
       </c>
-      <c r="H111">
+      <c r="I111">
         <v>1493</v>
       </c>
-      <c r="I111">
+      <c r="J111">
         <v>1894</v>
       </c>
-      <c r="J111">
+      <c r="K111">
         <v>1932</v>
       </c>
-      <c r="K111">
+      <c r="L111">
         <v>2049</v>
       </c>
-      <c r="L111">
+      <c r="M111">
         <v>2107</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112">
         <v>168</v>
       </c>
-      <c r="B112">
+      <c r="C112">
         <v>387</v>
       </c>
-      <c r="C112">
+      <c r="D112">
         <v>398</v>
       </c>
-      <c r="D112">
+      <c r="E112">
         <v>452</v>
       </c>
-      <c r="E112">
+      <c r="F112">
         <v>485</v>
       </c>
-      <c r="F112">
+      <c r="G112">
         <v>948</v>
       </c>
-      <c r="G112">
+      <c r="H112">
         <v>1309</v>
       </c>
-      <c r="H112">
+      <c r="I112">
         <v>1494</v>
       </c>
-      <c r="I112">
+      <c r="J112">
         <v>1574</v>
       </c>
-      <c r="J112">
+      <c r="K112">
         <v>1793</v>
       </c>
-      <c r="K112">
+      <c r="L112">
         <v>1944</v>
       </c>
-      <c r="L112">
+      <c r="M112">
         <v>2106</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113">
         <v>10</v>
       </c>
-      <c r="B113">
+      <c r="C113">
         <v>46</v>
       </c>
-      <c r="C113">
+      <c r="D113">
         <v>196</v>
       </c>
-      <c r="D113">
+      <c r="E113">
         <v>652</v>
       </c>
-      <c r="E113">
+      <c r="F113">
         <v>657</v>
       </c>
-      <c r="F113">
+      <c r="G113">
         <v>879</v>
       </c>
-      <c r="G113">
+      <c r="H113">
         <v>1206</v>
       </c>
-      <c r="H113">
+      <c r="I113">
         <v>1260</v>
       </c>
-      <c r="I113">
+      <c r="J113">
         <v>1496</v>
       </c>
-      <c r="J113">
+      <c r="K113">
         <v>1531</v>
       </c>
-      <c r="K113">
+      <c r="L113">
         <v>1747</v>
       </c>
-      <c r="L113">
+      <c r="M113">
         <v>1788</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114">
         <v>354</v>
       </c>
-      <c r="B114">
+      <c r="C114">
         <v>401</v>
       </c>
-      <c r="C114">
+      <c r="D114">
         <v>546</v>
       </c>
-      <c r="D114">
+      <c r="E114">
         <v>702</v>
       </c>
-      <c r="E114">
+      <c r="F114">
         <v>876</v>
       </c>
-      <c r="F114">
+      <c r="G114">
         <v>943</v>
       </c>
-      <c r="G114">
+      <c r="H114">
         <v>1020</v>
       </c>
-      <c r="H114">
+      <c r="I114">
         <v>1419</v>
       </c>
-      <c r="I114">
+      <c r="J114">
         <v>1490</v>
       </c>
-      <c r="J114">
+      <c r="K114">
         <v>1530</v>
       </c>
-      <c r="K114">
+      <c r="L114">
         <v>1554</v>
       </c>
-      <c r="L114">
+      <c r="M114">
         <v>1576</v>
       </c>
-      <c r="M114">
+      <c r="N114">
         <v>1707</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115">
         <v>6</v>
       </c>
-      <c r="B115">
+      <c r="C115">
         <v>666</v>
       </c>
-      <c r="C115">
+      <c r="D115">
         <v>707</v>
       </c>
-      <c r="D115">
+      <c r="E115">
         <v>782</v>
       </c>
-      <c r="E115">
+      <c r="F115">
         <v>790</v>
       </c>
-      <c r="F115">
+      <c r="G115">
         <v>841</v>
       </c>
-      <c r="G115">
+      <c r="H115">
         <v>844</v>
       </c>
-      <c r="H115">
+      <c r="I115">
         <v>1202</v>
       </c>
-      <c r="I115">
+      <c r="J115">
         <v>1213</v>
       </c>
-      <c r="J115">
+      <c r="K115">
         <v>1414</v>
       </c>
-      <c r="K115">
+      <c r="L115">
         <v>1663</v>
       </c>
-      <c r="L115">
+      <c r="M115">
         <v>1694</v>
       </c>
-      <c r="M115">
+      <c r="N115">
         <v>1715</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116">
         <v>27</v>
       </c>
-      <c r="B116">
+      <c r="C116">
         <v>613</v>
       </c>
-      <c r="C116">
+      <c r="D116">
         <v>683</v>
       </c>
-      <c r="D116">
+      <c r="E116">
         <v>765</v>
       </c>
-      <c r="E116">
+      <c r="F116">
         <v>991</v>
       </c>
-      <c r="F116">
+      <c r="G116">
         <v>1535</v>
       </c>
-      <c r="G116">
+      <c r="H116">
         <v>1539</v>
       </c>
-      <c r="H116">
+      <c r="I116">
         <v>1645</v>
       </c>
-      <c r="I116">
+      <c r="J116">
         <v>1664</v>
       </c>
-      <c r="J116">
+      <c r="K116">
         <v>1760</v>
       </c>
-      <c r="K116">
+      <c r="L116">
         <v>1925</v>
       </c>
-      <c r="L116">
+      <c r="M116">
         <v>1949</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117">
         <v>371</v>
       </c>
-      <c r="B117">
+      <c r="C117">
         <v>671</v>
       </c>
-      <c r="C117">
+      <c r="D117">
         <v>923</v>
       </c>
-      <c r="D117">
+      <c r="E117">
         <v>942</v>
       </c>
-      <c r="E117">
+      <c r="F117">
         <v>947</v>
       </c>
-      <c r="F117">
+      <c r="G117">
         <v>1258</v>
       </c>
-      <c r="G117">
+      <c r="H117">
         <v>1292</v>
       </c>
-      <c r="H117">
+      <c r="I117">
         <v>1616</v>
       </c>
-      <c r="I117">
+      <c r="J117">
         <v>1623</v>
       </c>
-      <c r="J117">
+      <c r="K117">
         <v>1713</v>
       </c>
-      <c r="K117">
+      <c r="L117">
         <v>1913</v>
       </c>
-      <c r="L117">
+      <c r="M117">
         <v>2070</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118">
         <v>98</v>
       </c>
-      <c r="B118">
+      <c r="C118">
         <v>104</v>
       </c>
-      <c r="C118">
+      <c r="D118">
         <v>509</v>
       </c>
-      <c r="D118">
+      <c r="E118">
         <v>610</v>
       </c>
-      <c r="E118">
+      <c r="F118">
         <v>690</v>
       </c>
-      <c r="F118">
+      <c r="G118">
         <v>694</v>
       </c>
-      <c r="G118">
+      <c r="H118">
         <v>721</v>
       </c>
-      <c r="H118">
+      <c r="I118">
         <v>821</v>
       </c>
-      <c r="I118">
+      <c r="J118">
         <v>1181</v>
       </c>
-      <c r="J118">
+      <c r="K118">
         <v>1188</v>
       </c>
-      <c r="K118">
+      <c r="L118">
         <v>1600</v>
       </c>
-      <c r="L118">
+      <c r="M118">
         <v>2061</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119">
         <v>338</v>
       </c>
-      <c r="B119">
+      <c r="C119">
         <v>341</v>
       </c>
-      <c r="C119">
+      <c r="D119">
         <v>343</v>
       </c>
-      <c r="D119">
+      <c r="E119">
         <v>344</v>
       </c>
-      <c r="E119">
+      <c r="F119">
         <v>345</v>
       </c>
-      <c r="F119">
+      <c r="G119">
         <v>347</v>
       </c>
-      <c r="G119">
+      <c r="H119">
         <v>415</v>
       </c>
-      <c r="H119">
+      <c r="I119">
         <v>496</v>
       </c>
-      <c r="I119">
+      <c r="J119">
         <v>530</v>
       </c>
-      <c r="J119">
+      <c r="K119">
         <v>1145</v>
       </c>
-      <c r="K119">
+      <c r="L119">
         <v>1174</v>
       </c>
-      <c r="L119">
+      <c r="M119">
         <v>1227</v>
       </c>
-      <c r="M119">
+      <c r="N119">
         <v>1410</v>
       </c>
-      <c r="N119">
+      <c r="O119">
         <v>2015</v>
       </c>
-      <c r="O119">
+      <c r="P119">
         <v>2073</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120">
         <v>162</v>
       </c>
-      <c r="B120">
+      <c r="C120">
         <v>624</v>
       </c>
-      <c r="C120">
+      <c r="D120">
         <v>701</v>
       </c>
-      <c r="D120">
+      <c r="E120">
         <v>752</v>
       </c>
-      <c r="E120">
+      <c r="F120">
         <v>762</v>
       </c>
-      <c r="F120">
+      <c r="G120">
         <v>807</v>
       </c>
-      <c r="G120">
+      <c r="H120">
         <v>818</v>
       </c>
-      <c r="H120">
+      <c r="I120">
         <v>850</v>
       </c>
-      <c r="I120">
+      <c r="J120">
         <v>1038</v>
       </c>
-      <c r="J120">
+      <c r="K120">
         <v>1555</v>
       </c>
-      <c r="K120">
+      <c r="L120">
         <v>1562</v>
       </c>
-      <c r="L120">
+      <c r="M120">
         <v>1964</v>
       </c>
-      <c r="M120">
+      <c r="N120">
         <v>2034</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121">
         <v>117</v>
       </c>
-      <c r="B121">
+      <c r="C121">
         <v>218</v>
       </c>
-      <c r="C121">
+      <c r="D121">
         <v>417</v>
       </c>
-      <c r="D121">
+      <c r="E121">
         <v>587</v>
       </c>
-      <c r="E121">
+      <c r="F121">
         <v>661</v>
       </c>
-      <c r="F121">
+      <c r="G121">
         <v>863</v>
       </c>
-      <c r="G121">
+      <c r="H121">
         <v>866</v>
       </c>
-      <c r="H121">
+      <c r="I121">
         <v>1237</v>
       </c>
-      <c r="I121">
+      <c r="J121">
         <v>1560</v>
       </c>
-      <c r="J121">
+      <c r="K121">
         <v>1751</v>
       </c>
-      <c r="K121">
+      <c r="L121">
         <v>1865</v>
       </c>
-      <c r="L121">
+      <c r="M121">
         <v>1888</v>
       </c>
-      <c r="M121">
+      <c r="N121">
         <v>1934</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122">
         <v>64</v>
       </c>
-      <c r="B122">
+      <c r="C122">
         <v>125</v>
       </c>
-      <c r="C122">
+      <c r="D122">
         <v>357</v>
       </c>
-      <c r="D122">
+      <c r="E122">
         <v>374</v>
       </c>
-      <c r="E122">
+      <c r="F122">
         <v>670</v>
       </c>
-      <c r="F122">
+      <c r="G122">
         <v>672</v>
       </c>
-      <c r="G122">
+      <c r="H122">
         <v>685</v>
       </c>
-      <c r="H122">
+      <c r="I122">
         <v>761</v>
       </c>
-      <c r="I122">
+      <c r="J122">
         <v>1059</v>
       </c>
-      <c r="J122">
+      <c r="K122">
         <v>1239</v>
       </c>
-      <c r="K122">
+      <c r="L122">
         <v>1817</v>
       </c>
-      <c r="L122">
+      <c r="M122">
         <v>1831</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123">
         <v>17</v>
       </c>
-      <c r="B123">
+      <c r="C123">
         <v>135</v>
       </c>
-      <c r="C123">
+      <c r="D123">
         <v>165</v>
       </c>
-      <c r="D123">
+      <c r="E123">
         <v>647</v>
       </c>
-      <c r="E123">
+      <c r="F123">
         <v>679</v>
       </c>
-      <c r="F123">
+      <c r="G123">
         <v>758</v>
       </c>
-      <c r="G123">
+      <c r="H123">
         <v>820</v>
       </c>
-      <c r="H123">
+      <c r="I123">
         <v>1009</v>
       </c>
-      <c r="I123">
+      <c r="J123">
         <v>1018</v>
       </c>
-      <c r="J123">
+      <c r="K123">
         <v>1086</v>
       </c>
-      <c r="K123">
+      <c r="L123">
         <v>2037</v>
       </c>
-      <c r="L123">
+      <c r="M123">
         <v>2054</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124">
         <v>32</v>
       </c>
-      <c r="B124">
+      <c r="C124">
         <v>474</v>
       </c>
-      <c r="C124">
+      <c r="D124">
         <v>646</v>
       </c>
-      <c r="D124">
+      <c r="E124">
         <v>689</v>
       </c>
-      <c r="E124">
+      <c r="F124">
         <v>1218</v>
       </c>
-      <c r="F124">
+      <c r="G124">
         <v>1283</v>
       </c>
-      <c r="G124">
+      <c r="H124">
         <v>1329</v>
       </c>
-      <c r="H124">
+      <c r="I124">
         <v>1400</v>
       </c>
-      <c r="I124">
+      <c r="J124">
         <v>1483</v>
       </c>
-      <c r="J124">
+      <c r="K124">
         <v>1565</v>
       </c>
-      <c r="K124">
+      <c r="L124">
         <v>1952</v>
       </c>
-      <c r="L124">
+      <c r="M124">
         <v>2014</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125">
         <v>267</v>
       </c>
-      <c r="B125">
+      <c r="C125">
         <v>315</v>
       </c>
-      <c r="C125">
+      <c r="D125">
         <v>333</v>
       </c>
-      <c r="D125">
+      <c r="E125">
         <v>402</v>
       </c>
-      <c r="E125">
+      <c r="F125">
         <v>520</v>
       </c>
-      <c r="F125">
+      <c r="G125">
         <v>648</v>
       </c>
-      <c r="G125">
+      <c r="H125">
         <v>1131</v>
       </c>
-      <c r="H125">
+      <c r="I125">
         <v>1286</v>
       </c>
-      <c r="I125">
+      <c r="J125">
         <v>1510</v>
       </c>
-      <c r="J125">
+      <c r="K125">
         <v>1654</v>
       </c>
-      <c r="K125">
+      <c r="L125">
         <v>1842</v>
       </c>
-      <c r="L125">
+      <c r="M125">
         <v>1970</v>
       </c>
-      <c r="M125">
+      <c r="N125">
         <v>2069</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126">
         <v>386</v>
       </c>
-      <c r="B126">
+      <c r="C126">
         <v>477</v>
       </c>
-      <c r="C126">
+      <c r="D126">
         <v>736</v>
       </c>
-      <c r="D126">
+      <c r="E126">
         <v>941</v>
       </c>
-      <c r="E126">
+      <c r="F126">
         <v>1132</v>
       </c>
-      <c r="F126">
+      <c r="G126">
         <v>1204</v>
       </c>
-      <c r="G126">
+      <c r="H126">
         <v>1262</v>
       </c>
-      <c r="H126">
+      <c r="I126">
         <v>1264</v>
       </c>
-      <c r="I126">
+      <c r="J126">
         <v>1271</v>
       </c>
-      <c r="J126">
+      <c r="K126">
         <v>1275</v>
       </c>
-      <c r="K126">
+      <c r="L126">
         <v>1382</v>
       </c>
-      <c r="L126">
+      <c r="M126">
         <v>1883</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127">
         <v>35</v>
       </c>
-      <c r="B127">
+      <c r="C127">
         <v>107</v>
       </c>
-      <c r="C127">
+      <c r="D127">
         <v>124</v>
       </c>
-      <c r="D127">
+      <c r="E127">
         <v>621</v>
       </c>
-      <c r="E127">
+      <c r="F127">
         <v>874</v>
       </c>
-      <c r="F127">
+      <c r="G127">
         <v>875</v>
       </c>
-      <c r="G127">
+      <c r="H127">
         <v>1184</v>
       </c>
-      <c r="H127">
+      <c r="I127">
         <v>1465</v>
       </c>
-      <c r="I127">
+      <c r="J127">
         <v>1597</v>
       </c>
-      <c r="J127">
+      <c r="K127">
         <v>1604</v>
       </c>
-      <c r="K127">
+      <c r="L127">
         <v>1705</v>
       </c>
-      <c r="L127">
+      <c r="M127">
         <v>1918</v>
       </c>
-      <c r="M127">
+      <c r="N127">
         <v>1931</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128">
         <v>42</v>
       </c>
-      <c r="B128">
+      <c r="C128">
         <v>103</v>
       </c>
-      <c r="C128">
+      <c r="D128">
         <v>209</v>
       </c>
-      <c r="D128">
+      <c r="E128">
         <v>245</v>
       </c>
-      <c r="E128">
+      <c r="F128">
         <v>739</v>
       </c>
-      <c r="F128">
+      <c r="G128">
         <v>1291</v>
       </c>
-      <c r="G128">
+      <c r="H128">
         <v>1306</v>
       </c>
-      <c r="H128">
+      <c r="I128">
         <v>1424</v>
       </c>
-      <c r="I128">
+      <c r="J128">
         <v>1434</v>
       </c>
-      <c r="J128">
+      <c r="K128">
         <v>1735</v>
       </c>
-      <c r="K128">
+      <c r="L128">
         <v>1775</v>
       </c>
-      <c r="L128">
+      <c r="M128">
         <v>1937</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129">
         <v>53</v>
       </c>
-      <c r="B129">
+      <c r="C129">
         <v>148</v>
       </c>
-      <c r="C129">
+      <c r="D129">
         <v>160</v>
       </c>
-      <c r="D129">
+      <c r="E129">
         <v>288</v>
       </c>
-      <c r="E129">
+      <c r="F129">
         <v>296</v>
       </c>
-      <c r="F129">
+      <c r="G129">
         <v>407</v>
       </c>
-      <c r="G129">
+      <c r="H129">
         <v>1007</v>
       </c>
-      <c r="H129">
+      <c r="I129">
         <v>1008</v>
       </c>
-      <c r="I129">
+      <c r="J129">
         <v>1088</v>
       </c>
-      <c r="J129">
+      <c r="K129">
         <v>1091</v>
       </c>
-      <c r="K129">
+      <c r="L129">
         <v>1350</v>
       </c>
-      <c r="L129">
+      <c r="M129">
         <v>1980</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130">
         <v>111</v>
       </c>
-      <c r="B130">
+      <c r="C130">
         <v>118</v>
       </c>
-      <c r="C130">
+      <c r="D130">
         <v>213</v>
       </c>
-      <c r="D130">
+      <c r="E130">
         <v>275</v>
       </c>
-      <c r="E130">
+      <c r="F130">
         <v>327</v>
       </c>
-      <c r="F130">
+      <c r="G130">
         <v>438</v>
       </c>
-      <c r="G130">
+      <c r="H130">
         <v>644</v>
       </c>
-      <c r="H130">
+      <c r="I130">
         <v>1387</v>
       </c>
-      <c r="I130">
+      <c r="J130">
         <v>1653</v>
       </c>
-      <c r="J130">
+      <c r="K130">
         <v>2027</v>
       </c>
-      <c r="K130">
+      <c r="L130">
         <v>2039</v>
       </c>
-      <c r="L130">
+      <c r="M130">
         <v>2087</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131">
         <v>149</v>
       </c>
-      <c r="B131">
+      <c r="C131">
         <v>301</v>
       </c>
-      <c r="C131">
+      <c r="D131">
         <v>483</v>
       </c>
-      <c r="D131">
+      <c r="E131">
         <v>581</v>
       </c>
-      <c r="E131">
+      <c r="F131">
         <v>595</v>
       </c>
-      <c r="F131">
+      <c r="G131">
         <v>642</v>
       </c>
-      <c r="G131">
+      <c r="H131">
         <v>723</v>
       </c>
-      <c r="H131">
+      <c r="I131">
         <v>734</v>
       </c>
-      <c r="I131">
+      <c r="J131">
         <v>882</v>
       </c>
-      <c r="J131">
+      <c r="K131">
         <v>913</v>
       </c>
-      <c r="K131">
+      <c r="L131">
         <v>1546</v>
       </c>
-      <c r="L131">
+      <c r="M131">
         <v>1585</v>
       </c>
-      <c r="M131">
+      <c r="N131">
         <v>1731</v>
       </c>
-      <c r="N131">
+      <c r="O131">
         <v>1852</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132">
         <v>482</v>
       </c>
-      <c r="B132">
+      <c r="C132">
         <v>717</v>
       </c>
-      <c r="C132">
+      <c r="D132">
         <v>904</v>
       </c>
-      <c r="D132">
+      <c r="E132">
         <v>1004</v>
       </c>
-      <c r="E132">
+      <c r="F132">
         <v>1006</v>
       </c>
-      <c r="F132">
+      <c r="G132">
         <v>1366</v>
       </c>
-      <c r="G132">
+      <c r="H132">
         <v>1374</v>
       </c>
-      <c r="H132">
+      <c r="I132">
         <v>1503</v>
       </c>
-      <c r="I132">
+      <c r="J132">
         <v>1512</v>
       </c>
-      <c r="J132">
+      <c r="K132">
         <v>1624</v>
       </c>
-      <c r="K132">
+      <c r="L132">
         <v>1716</v>
       </c>
-      <c r="L132">
+      <c r="M132">
         <v>1740</v>
       </c>
-      <c r="M132">
+      <c r="N132">
         <v>1972</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133">
         <v>1</v>
       </c>
-      <c r="B133">
+      <c r="C133">
         <v>437</v>
       </c>
-      <c r="C133">
+      <c r="D133">
         <v>629</v>
       </c>
-      <c r="D133">
+      <c r="E133">
         <v>1005</v>
       </c>
-      <c r="E133">
+      <c r="F133">
         <v>1023</v>
       </c>
-      <c r="F133">
+      <c r="G133">
         <v>1280</v>
       </c>
-      <c r="G133">
+      <c r="H133">
         <v>1558</v>
       </c>
-      <c r="H133">
+      <c r="I133">
         <v>1700</v>
       </c>
-      <c r="I133">
+      <c r="J133">
         <v>1928</v>
       </c>
-      <c r="J133">
+      <c r="K133">
         <v>1986</v>
       </c>
-      <c r="K133">
+      <c r="L133">
         <v>2026</v>
       </c>
-      <c r="L133">
+      <c r="M133">
         <v>2068</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134">
         <v>9</v>
       </c>
-      <c r="B134">
+      <c r="C134">
         <v>254</v>
       </c>
-      <c r="C134">
+      <c r="D134">
         <v>355</v>
       </c>
-      <c r="D134">
+      <c r="E134">
         <v>905</v>
       </c>
-      <c r="E134">
+      <c r="F134">
         <v>1142</v>
       </c>
-      <c r="F134">
+      <c r="G134">
         <v>1200</v>
       </c>
-      <c r="G134">
+      <c r="H134">
         <v>1215</v>
       </c>
-      <c r="H134">
+      <c r="I134">
         <v>1592</v>
       </c>
-      <c r="I134">
+      <c r="J134">
         <v>1810</v>
       </c>
-      <c r="J134">
+      <c r="K134">
         <v>1900</v>
       </c>
-      <c r="K134">
+      <c r="L134">
         <v>1916</v>
       </c>
-      <c r="L134">
+      <c r="M134">
         <v>2016</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135">
         <v>145</v>
       </c>
-      <c r="B135">
+      <c r="C135">
         <v>362</v>
       </c>
-      <c r="C135">
+      <c r="D135">
         <v>635</v>
       </c>
-      <c r="D135">
+      <c r="E135">
         <v>725</v>
       </c>
-      <c r="E135">
+      <c r="F135">
         <v>811</v>
       </c>
-      <c r="F135">
+      <c r="G135">
         <v>1093</v>
       </c>
-      <c r="G135">
+      <c r="H135">
         <v>1095</v>
       </c>
-      <c r="H135">
+      <c r="I135">
         <v>1097</v>
       </c>
-      <c r="I135">
+      <c r="J135">
         <v>1417</v>
       </c>
-      <c r="J135">
+      <c r="K135">
         <v>1420</v>
       </c>
-      <c r="K135">
+      <c r="L135">
         <v>1660</v>
       </c>
-      <c r="L135">
+      <c r="M135">
         <v>1721</v>
       </c>
-      <c r="M135">
+      <c r="N135">
         <v>2023</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136">
         <v>152</v>
       </c>
-      <c r="B136">
+      <c r="C136">
         <v>435</v>
       </c>
-      <c r="C136">
+      <c r="D136">
         <v>680</v>
       </c>
-      <c r="D136">
+      <c r="E136">
         <v>1316</v>
       </c>
-      <c r="E136">
+      <c r="F136">
         <v>1370</v>
       </c>
-      <c r="F136">
+      <c r="G136">
         <v>1401</v>
       </c>
-      <c r="G136">
+      <c r="H136">
         <v>1635</v>
       </c>
-      <c r="H136">
+      <c r="I136">
         <v>1875</v>
       </c>
-      <c r="I136">
+      <c r="J136">
         <v>1991</v>
       </c>
-      <c r="J136">
+      <c r="K136">
         <v>1992</v>
       </c>
-      <c r="K136">
+      <c r="L136">
         <v>1994</v>
       </c>
-      <c r="L136">
+      <c r="M136">
         <v>1995</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137">
         <v>62</v>
       </c>
-      <c r="B137">
+      <c r="C137">
         <v>191</v>
       </c>
-      <c r="C137">
+      <c r="D137">
         <v>223</v>
       </c>
-      <c r="D137">
+      <c r="E137">
         <v>662</v>
       </c>
-      <c r="E137">
+      <c r="F137">
         <v>929</v>
       </c>
-      <c r="F137">
+      <c r="G137">
         <v>994</v>
       </c>
-      <c r="G137">
+      <c r="H137">
         <v>1083</v>
       </c>
-      <c r="H137">
+      <c r="I137">
         <v>1100</v>
       </c>
-      <c r="I137">
+      <c r="J137">
         <v>1217</v>
       </c>
-      <c r="J137">
+      <c r="K137">
         <v>1443</v>
       </c>
-      <c r="K137">
+      <c r="L137">
         <v>1573</v>
       </c>
-      <c r="L137">
+      <c r="M137">
         <v>1598</v>
       </c>
-      <c r="M137">
+      <c r="N137">
         <v>1766</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138">
         <v>44</v>
       </c>
-      <c r="B138">
+      <c r="C138">
         <v>219</v>
       </c>
-      <c r="C138">
+      <c r="D138">
         <v>469</v>
       </c>
-      <c r="D138">
+      <c r="E138">
         <v>578</v>
       </c>
-      <c r="E138">
+      <c r="F138">
         <v>785</v>
       </c>
-      <c r="F138">
+      <c r="G138">
         <v>884</v>
       </c>
-      <c r="G138">
+      <c r="H138">
         <v>967</v>
       </c>
-      <c r="H138">
+      <c r="I138">
         <v>981</v>
       </c>
-      <c r="I138">
+      <c r="J138">
         <v>1140</v>
       </c>
-      <c r="J138">
+      <c r="K138">
         <v>1203</v>
       </c>
-      <c r="K138">
+      <c r="L138">
         <v>1248</v>
       </c>
-      <c r="L138">
+      <c r="M138">
         <v>1570</v>
       </c>
-      <c r="M138">
+      <c r="N138">
         <v>1692</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139">
         <v>180</v>
       </c>
-      <c r="B139">
+      <c r="C139">
         <v>390</v>
       </c>
-      <c r="C139">
+      <c r="D139">
         <v>441</v>
       </c>
-      <c r="D139">
+      <c r="E139">
         <v>549</v>
       </c>
-      <c r="E139">
+      <c r="F139">
         <v>567</v>
       </c>
-      <c r="F139">
+      <c r="G139">
         <v>619</v>
       </c>
-      <c r="G139">
+      <c r="H139">
         <v>633</v>
       </c>
-      <c r="H139">
+      <c r="I139">
         <v>907</v>
       </c>
-      <c r="I139">
+      <c r="J139">
         <v>987</v>
       </c>
-      <c r="J139">
+      <c r="K139">
         <v>1021</v>
       </c>
-      <c r="K139">
+      <c r="L139">
         <v>1326</v>
       </c>
-      <c r="L139">
+      <c r="M139">
         <v>1527</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140">
         <v>173</v>
       </c>
-      <c r="B140">
+      <c r="C140">
         <v>175</v>
       </c>
-      <c r="C140">
+      <c r="D140">
         <v>993</v>
       </c>
-      <c r="D140">
+      <c r="E140">
         <v>1129</v>
       </c>
-      <c r="E140">
+      <c r="F140">
         <v>1327</v>
       </c>
-      <c r="F140">
+      <c r="G140">
         <v>1515</v>
       </c>
-      <c r="G140">
+      <c r="H140">
         <v>1765</v>
       </c>
-      <c r="H140">
+      <c r="I140">
         <v>1851</v>
       </c>
-      <c r="I140">
+      <c r="J140">
         <v>1880</v>
       </c>
-      <c r="J140">
+      <c r="K140">
         <v>2052</v>
       </c>
-      <c r="K140">
+      <c r="L140">
         <v>2096</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141">
         <v>277</v>
       </c>
-      <c r="B141">
+      <c r="C141">
         <v>416</v>
       </c>
-      <c r="C141">
+      <c r="D141">
         <v>470</v>
       </c>
-      <c r="D141">
+      <c r="E141">
         <v>478</v>
       </c>
-      <c r="E141">
+      <c r="F141">
         <v>798</v>
       </c>
-      <c r="F141">
+      <c r="G141">
         <v>836</v>
       </c>
-      <c r="G141">
+      <c r="H141">
         <v>914</v>
       </c>
-      <c r="H141">
+      <c r="I141">
         <v>1416</v>
       </c>
-      <c r="I141">
+      <c r="J141">
         <v>1437</v>
       </c>
-      <c r="J141">
+      <c r="K141">
         <v>1528</v>
       </c>
-      <c r="K141">
+      <c r="L141">
         <v>1533</v>
       </c>
-      <c r="L141">
+      <c r="M141">
         <v>1564</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142">
         <v>406</v>
       </c>
-      <c r="B142">
+      <c r="C142">
         <v>432</v>
       </c>
-      <c r="C142">
+      <c r="D142">
         <v>556</v>
       </c>
-      <c r="D142">
+      <c r="E142">
         <v>705</v>
       </c>
-      <c r="E142">
+      <c r="F142">
         <v>751</v>
       </c>
-      <c r="F142">
+      <c r="G142">
         <v>828</v>
       </c>
-      <c r="G142">
+      <c r="H142">
         <v>895</v>
       </c>
-      <c r="H142">
+      <c r="I142">
         <v>900</v>
       </c>
-      <c r="I142">
+      <c r="J142">
         <v>1118</v>
       </c>
-      <c r="J142">
+      <c r="K142">
         <v>1265</v>
       </c>
-      <c r="K142">
+      <c r="L142">
         <v>1475</v>
       </c>
-      <c r="L142">
+      <c r="M142">
         <v>1909</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143">
         <v>34</v>
       </c>
-      <c r="B143">
+      <c r="C143">
         <v>143</v>
       </c>
-      <c r="C143">
+      <c r="D143">
         <v>150</v>
       </c>
-      <c r="D143">
+      <c r="E143">
         <v>155</v>
       </c>
-      <c r="E143">
+      <c r="F143">
         <v>251</v>
       </c>
-      <c r="F143">
+      <c r="G143">
         <v>573</v>
       </c>
-      <c r="G143">
+      <c r="H143">
         <v>917</v>
       </c>
-      <c r="H143">
+      <c r="I143">
         <v>1033</v>
       </c>
-      <c r="I143">
+      <c r="J143">
         <v>1233</v>
       </c>
-      <c r="J143">
+      <c r="K143">
         <v>1317</v>
       </c>
-      <c r="K143">
+      <c r="L143">
         <v>1552</v>
       </c>
-      <c r="L143">
+      <c r="M143">
         <v>1553</v>
       </c>
-      <c r="M143">
+      <c r="N143">
         <v>1833</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144">
         <v>43</v>
       </c>
-      <c r="B144">
+      <c r="C144">
         <v>190</v>
       </c>
-      <c r="C144">
+      <c r="D144">
         <v>227</v>
       </c>
-      <c r="D144">
+      <c r="E144">
         <v>748</v>
       </c>
-      <c r="E144">
+      <c r="F144">
         <v>998</v>
       </c>
-      <c r="F144">
+      <c r="G144">
         <v>1000</v>
       </c>
-      <c r="G144">
+      <c r="H144">
         <v>1463</v>
       </c>
-      <c r="H144">
+      <c r="I144">
         <v>1467</v>
       </c>
-      <c r="I144">
+      <c r="J144">
         <v>1755</v>
       </c>
-      <c r="J144">
+      <c r="K144">
         <v>1961</v>
       </c>
-      <c r="K144">
+      <c r="L144">
         <v>1982</v>
       </c>
-      <c r="L144">
+      <c r="M144">
         <v>2000</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145">
         <v>74</v>
       </c>
-      <c r="B145">
+      <c r="C145">
         <v>1147</v>
       </c>
-      <c r="C145">
+      <c r="D145">
         <v>1255</v>
       </c>
-      <c r="D145">
+      <c r="E145">
         <v>1360</v>
       </c>
-      <c r="E145">
+      <c r="F145">
         <v>1368</v>
       </c>
-      <c r="F145">
+      <c r="G145">
         <v>1789</v>
       </c>
-      <c r="G145">
+      <c r="H145">
         <v>1790</v>
       </c>
-      <c r="H145">
+      <c r="I145">
         <v>1791</v>
       </c>
-      <c r="I145">
+      <c r="J145">
         <v>1792</v>
       </c>
-      <c r="J145">
+      <c r="K145">
         <v>1795</v>
       </c>
-      <c r="K145">
+      <c r="L145">
         <v>1796</v>
       </c>
-      <c r="L145">
+      <c r="M145">
         <v>1797</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146">
         <v>484</v>
       </c>
-      <c r="B146">
+      <c r="C146">
         <v>663</v>
       </c>
-      <c r="C146">
+      <c r="D146">
         <v>793</v>
       </c>
-      <c r="D146">
+      <c r="E146">
         <v>946</v>
       </c>
-      <c r="E146">
+      <c r="F146">
         <v>976</v>
       </c>
-      <c r="F146">
+      <c r="G146">
         <v>1128</v>
       </c>
-      <c r="G146">
+      <c r="H146">
         <v>1208</v>
       </c>
-      <c r="H146">
+      <c r="I146">
         <v>1228</v>
       </c>
-      <c r="I146">
+      <c r="J146">
         <v>1299</v>
       </c>
-      <c r="J146">
+      <c r="K146">
         <v>1575</v>
       </c>
-      <c r="K146">
+      <c r="L146">
         <v>1999</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147">
         <v>316</v>
       </c>
-      <c r="B147">
+      <c r="C147">
         <v>321</v>
       </c>
-      <c r="C147">
+      <c r="D147">
         <v>1201</v>
       </c>
-      <c r="D147">
+      <c r="E147">
         <v>1272</v>
       </c>
-      <c r="E147">
+      <c r="F147">
         <v>1320</v>
       </c>
-      <c r="F147">
+      <c r="G147">
         <v>1440</v>
       </c>
-      <c r="G147">
+      <c r="H147">
         <v>1445</v>
       </c>
-      <c r="H147">
+      <c r="I147">
         <v>1484</v>
       </c>
-      <c r="I147">
+      <c r="J147">
         <v>1518</v>
       </c>
-      <c r="J147">
+      <c r="K147">
         <v>1534</v>
       </c>
-      <c r="K147">
+      <c r="L147">
         <v>1636</v>
       </c>
-      <c r="L147">
+      <c r="M147">
         <v>1794</v>
       </c>
-      <c r="M147">
+      <c r="N147">
         <v>1798</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148">
         <v>85</v>
       </c>
-      <c r="B148">
+      <c r="C148">
         <v>326</v>
       </c>
-      <c r="C148">
+      <c r="D148">
         <v>659</v>
       </c>
-      <c r="D148">
+      <c r="E148">
         <v>809</v>
       </c>
-      <c r="E148">
+      <c r="F148">
         <v>843</v>
       </c>
-      <c r="F148">
+      <c r="G148">
         <v>870</v>
       </c>
-      <c r="G148">
+      <c r="H148">
         <v>1268</v>
       </c>
-      <c r="H148">
+      <c r="I148">
         <v>1279</v>
       </c>
-      <c r="I148">
+      <c r="J148">
         <v>1398</v>
       </c>
-      <c r="J148">
+      <c r="K148">
         <v>1462</v>
       </c>
-      <c r="K148">
+      <c r="L148">
         <v>1864</v>
       </c>
-      <c r="L148">
+      <c r="M148">
         <v>2008</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149">
         <v>56</v>
       </c>
-      <c r="B149">
+      <c r="C149">
         <v>63</v>
       </c>
-      <c r="C149">
+      <c r="D149">
         <v>174</v>
       </c>
-      <c r="D149">
+      <c r="E149">
         <v>377</v>
       </c>
-      <c r="E149">
+      <c r="F149">
         <v>557</v>
       </c>
-      <c r="F149">
+      <c r="G149">
         <v>579</v>
       </c>
-      <c r="G149">
+      <c r="H149">
         <v>616</v>
       </c>
-      <c r="H149">
+      <c r="I149">
         <v>1056</v>
       </c>
-      <c r="I149">
+      <c r="J149">
         <v>1154</v>
       </c>
-      <c r="J149">
+      <c r="K149">
         <v>1602</v>
       </c>
-      <c r="K149">
+      <c r="L149">
         <v>1710</v>
       </c>
-      <c r="L149">
+      <c r="M149">
         <v>1870</v>
       </c>
-      <c r="M149">
+      <c r="N149">
         <v>2010</v>
       </c>
-      <c r="N149">
+      <c r="O149">
         <v>2018</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150">
         <v>11</v>
       </c>
-      <c r="B150">
+      <c r="C150">
         <v>131</v>
       </c>
-      <c r="C150">
+      <c r="D150">
         <v>750</v>
       </c>
-      <c r="D150">
+      <c r="E150">
         <v>1094</v>
       </c>
-      <c r="E150">
+      <c r="F150">
         <v>1110</v>
       </c>
-      <c r="F150">
+      <c r="G150">
         <v>1113</v>
       </c>
-      <c r="G150">
+      <c r="H150">
         <v>1163</v>
       </c>
-      <c r="H150">
+      <c r="I150">
         <v>1240</v>
       </c>
-      <c r="I150">
+      <c r="J150">
         <v>1569</v>
       </c>
-      <c r="J150">
+      <c r="K150">
         <v>1836</v>
       </c>
-      <c r="K150">
+      <c r="L150">
         <v>2043</v>
       </c>
-      <c r="L150">
+      <c r="M150">
         <v>2082</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151">
         <v>4</v>
       </c>
-      <c r="B151">
+      <c r="C151">
         <v>214</v>
       </c>
-      <c r="C151">
+      <c r="D151">
         <v>366</v>
       </c>
-      <c r="D151">
+      <c r="E151">
         <v>611</v>
       </c>
-      <c r="E151">
+      <c r="F151">
         <v>740</v>
       </c>
-      <c r="F151">
+      <c r="G151">
         <v>775</v>
       </c>
-      <c r="G151">
+      <c r="H151">
         <v>814</v>
       </c>
-      <c r="H151">
+      <c r="I151">
         <v>815</v>
       </c>
-      <c r="I151">
+      <c r="J151">
         <v>899</v>
       </c>
-      <c r="J151">
+      <c r="K151">
         <v>990</v>
       </c>
-      <c r="K151">
+      <c r="L151">
         <v>1373</v>
       </c>
-      <c r="L151">
+      <c r="M151">
         <v>1594</v>
       </c>
-      <c r="M151">
+      <c r="N151">
         <v>1907</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152">
         <v>346</v>
       </c>
-      <c r="B152">
+      <c r="C152">
         <v>356</v>
       </c>
-      <c r="C152">
+      <c r="D152">
         <v>421</v>
       </c>
-      <c r="D152">
+      <c r="E152">
         <v>431</v>
       </c>
-      <c r="E152">
+      <c r="F152">
         <v>830</v>
       </c>
-      <c r="F152">
+      <c r="G152">
         <v>1111</v>
       </c>
-      <c r="G152">
+      <c r="H152">
         <v>1312</v>
       </c>
-      <c r="H152">
+      <c r="I152">
         <v>1397</v>
       </c>
-      <c r="I152">
+      <c r="J152">
         <v>1404</v>
       </c>
-      <c r="J152">
+      <c r="K152">
         <v>1724</v>
       </c>
-      <c r="K152">
+      <c r="L152">
         <v>1744</v>
       </c>
-      <c r="L152">
+      <c r="M152">
         <v>1954</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153">
         <v>259</v>
       </c>
-      <c r="B153">
+      <c r="C153">
         <v>339</v>
       </c>
-      <c r="C153">
+      <c r="D153">
         <v>378</v>
       </c>
-      <c r="D153">
+      <c r="E153">
         <v>399</v>
       </c>
-      <c r="E153">
+      <c r="F153">
         <v>655</v>
       </c>
-      <c r="F153">
+      <c r="G153">
         <v>860</v>
       </c>
-      <c r="G153">
+      <c r="H153">
         <v>928</v>
       </c>
-      <c r="H153">
+      <c r="I153">
         <v>932</v>
       </c>
-      <c r="I153">
+      <c r="J153">
         <v>933</v>
       </c>
-      <c r="J153">
+      <c r="K153">
         <v>934</v>
       </c>
-      <c r="K153">
+      <c r="L153">
         <v>936</v>
       </c>
-      <c r="L153">
+      <c r="M153">
         <v>938</v>
       </c>
-      <c r="M153">
+      <c r="N153">
         <v>1193</v>
       </c>
-      <c r="N153">
+      <c r="O153">
         <v>1773</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154">
         <v>60</v>
       </c>
-      <c r="B154">
+      <c r="C154">
         <v>61</v>
       </c>
-      <c r="C154">
+      <c r="D154">
         <v>179</v>
       </c>
-      <c r="D154">
+      <c r="E154">
         <v>323</v>
       </c>
-      <c r="E154">
+      <c r="F154">
         <v>630</v>
       </c>
-      <c r="F154">
+      <c r="G154">
         <v>1015</v>
       </c>
-      <c r="G154">
+      <c r="H154">
         <v>1249</v>
       </c>
-      <c r="H154">
+      <c r="I154">
         <v>1509</v>
       </c>
-      <c r="I154">
+      <c r="J154">
         <v>1549</v>
       </c>
-      <c r="J154">
+      <c r="K154">
         <v>1806</v>
       </c>
-      <c r="K154">
+      <c r="L154">
         <v>1885</v>
       </c>
-      <c r="L154">
+      <c r="M154">
         <v>2020</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155">
         <v>274</v>
       </c>
-      <c r="B155">
+      <c r="C155">
         <v>283</v>
       </c>
-      <c r="C155">
+      <c r="D155">
         <v>331</v>
       </c>
-      <c r="D155">
+      <c r="E155">
         <v>468</v>
       </c>
-      <c r="E155">
+      <c r="F155">
         <v>493</v>
       </c>
-      <c r="F155">
+      <c r="G155">
         <v>606</v>
       </c>
-      <c r="G155">
+      <c r="H155">
         <v>1160</v>
       </c>
-      <c r="H155">
+      <c r="I155">
         <v>1657</v>
       </c>
-      <c r="I155">
+      <c r="J155">
         <v>1845</v>
       </c>
-      <c r="J155">
+      <c r="K155">
         <v>1988</v>
       </c>
-      <c r="K155">
+      <c r="L155">
         <v>1989</v>
       </c>
-      <c r="L155">
+      <c r="M155">
         <v>2084</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156">
         <v>183</v>
       </c>
-      <c r="B156">
+      <c r="C156">
         <v>200</v>
       </c>
-      <c r="C156">
+      <c r="D156">
         <v>400</v>
       </c>
-      <c r="D156">
+      <c r="E156">
         <v>519</v>
       </c>
-      <c r="E156">
+      <c r="F156">
         <v>691</v>
       </c>
-      <c r="F156">
+      <c r="G156">
         <v>834</v>
       </c>
-      <c r="G156">
+      <c r="H156">
         <v>955</v>
       </c>
-      <c r="H156">
+      <c r="I156">
         <v>972</v>
       </c>
-      <c r="I156">
+      <c r="J156">
         <v>977</v>
       </c>
-      <c r="J156">
+      <c r="K156">
         <v>1287</v>
       </c>
-      <c r="K156">
+      <c r="L156">
         <v>1774</v>
       </c>
-      <c r="L156">
+      <c r="M156">
         <v>1950</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157">
         <v>264</v>
       </c>
-      <c r="B157">
+      <c r="C157">
         <v>559</v>
       </c>
-      <c r="C157">
+      <c r="D157">
         <v>684</v>
       </c>
-      <c r="D157">
+      <c r="E157">
         <v>709</v>
       </c>
-      <c r="E157">
+      <c r="F157">
         <v>797</v>
       </c>
-      <c r="F157">
+      <c r="G157">
         <v>975</v>
       </c>
-      <c r="G157">
+      <c r="H157">
         <v>1050</v>
       </c>
-      <c r="H157">
+      <c r="I157">
         <v>1521</v>
       </c>
-      <c r="I157">
+      <c r="J157">
         <v>1522</v>
       </c>
-      <c r="J157">
+      <c r="K157">
         <v>1622</v>
       </c>
-      <c r="K157">
+      <c r="L157">
         <v>1729</v>
       </c>
-      <c r="L157">
+      <c r="M157">
         <v>1815</v>
       </c>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158">
         <v>186</v>
       </c>
-      <c r="B158">
+      <c r="C158">
         <v>446</v>
       </c>
-      <c r="C158">
+      <c r="D158">
         <v>480</v>
       </c>
-      <c r="D158">
+      <c r="E158">
         <v>759</v>
       </c>
-      <c r="E158">
+      <c r="F158">
         <v>805</v>
       </c>
-      <c r="F158">
+      <c r="G158">
         <v>808</v>
       </c>
-      <c r="G158">
+      <c r="H158">
         <v>980</v>
       </c>
-      <c r="H158">
+      <c r="I158">
         <v>985</v>
       </c>
-      <c r="I158">
+      <c r="J158">
         <v>1187</v>
       </c>
-      <c r="J158">
+      <c r="K158">
         <v>1469</v>
       </c>
-      <c r="K158">
+      <c r="L158">
         <v>1748</v>
       </c>
-      <c r="L158">
+      <c r="M158">
         <v>1985</v>
       </c>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159">
         <v>50</v>
       </c>
-      <c r="B159">
+      <c r="C159">
         <v>51</v>
       </c>
-      <c r="C159">
+      <c r="D159">
         <v>110</v>
       </c>
-      <c r="D159">
+      <c r="E159">
         <v>215</v>
       </c>
-      <c r="E159">
+      <c r="F159">
         <v>395</v>
       </c>
-      <c r="F159">
+      <c r="G159">
         <v>1046</v>
       </c>
-      <c r="G159">
+      <c r="H159">
         <v>1180</v>
       </c>
-      <c r="H159">
+      <c r="I159">
         <v>1219</v>
       </c>
-      <c r="I159">
+      <c r="J159">
         <v>1435</v>
       </c>
-      <c r="J159">
+      <c r="K159">
         <v>1743</v>
       </c>
-      <c r="K159">
+      <c r="L159">
         <v>1877</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160">
         <v>137</v>
       </c>
-      <c r="B160">
+      <c r="C160">
         <v>596</v>
       </c>
-      <c r="C160">
+      <c r="D160">
         <v>623</v>
       </c>
-      <c r="D160">
+      <c r="E160">
         <v>961</v>
       </c>
-      <c r="E160">
+      <c r="F160">
         <v>1054</v>
       </c>
-      <c r="F160">
+      <c r="G160">
         <v>1353</v>
       </c>
-      <c r="G160">
+      <c r="H160">
         <v>1495</v>
       </c>
-      <c r="H160">
+      <c r="I160">
         <v>1617</v>
       </c>
-      <c r="I160">
+      <c r="J160">
         <v>1656</v>
       </c>
-      <c r="J160">
+      <c r="K160">
         <v>1838</v>
       </c>
-      <c r="K160">
+      <c r="L160">
         <v>1839</v>
       </c>
-      <c r="L160">
+      <c r="M160">
         <v>1892</v>
       </c>
-      <c r="M160">
+      <c r="N160">
         <v>1919</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161">
         <v>157</v>
       </c>
-      <c r="B161">
+      <c r="C161">
         <v>380</v>
       </c>
-      <c r="C161">
+      <c r="D161">
         <v>455</v>
       </c>
-      <c r="D161">
+      <c r="E161">
         <v>513</v>
       </c>
-      <c r="E161">
+      <c r="F161">
         <v>676</v>
       </c>
-      <c r="F161">
+      <c r="G161">
         <v>804</v>
       </c>
-      <c r="G161">
+      <c r="H161">
         <v>823</v>
       </c>
-      <c r="H161">
+      <c r="I161">
         <v>1116</v>
       </c>
-      <c r="I161">
+      <c r="J161">
         <v>1563</v>
       </c>
-      <c r="J161">
+      <c r="K161">
         <v>1584</v>
       </c>
-      <c r="K161">
+      <c r="L161">
         <v>1708</v>
       </c>
-      <c r="L161">
+      <c r="M161">
         <v>1809</v>
       </c>
-      <c r="M161">
+      <c r="N161">
         <v>1903</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A162">
+        <v>161</v>
+      </c>
+      <c r="B162">
         <v>2</v>
       </c>
-      <c r="B162">
+      <c r="C162">
         <v>21</v>
       </c>
-      <c r="C162">
+      <c r="D162">
         <v>30</v>
       </c>
-      <c r="D162">
+      <c r="E162">
         <v>164</v>
       </c>
-      <c r="E162">
+      <c r="F162">
         <v>418</v>
       </c>
-      <c r="F162">
+      <c r="G162">
         <v>857</v>
       </c>
-      <c r="G162">
+      <c r="H162">
         <v>965</v>
       </c>
-      <c r="H162">
+      <c r="I162">
         <v>988</v>
       </c>
-      <c r="I162">
+      <c r="J162">
         <v>1190</v>
       </c>
-      <c r="J162">
+      <c r="K162">
         <v>1224</v>
       </c>
-      <c r="K162">
+      <c r="L162">
         <v>1245</v>
       </c>
-      <c r="L162">
+      <c r="M162">
         <v>1763</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A163">
+        <v>162</v>
+      </c>
+      <c r="B163">
         <v>318</v>
       </c>
-      <c r="B163">
+      <c r="C163">
         <v>510</v>
       </c>
-      <c r="C163">
+      <c r="D163">
         <v>598</v>
       </c>
-      <c r="D163">
+      <c r="E163">
         <v>1308</v>
       </c>
-      <c r="E163">
+      <c r="F163">
         <v>1557</v>
       </c>
-      <c r="F163">
+      <c r="G163">
         <v>1559</v>
       </c>
-      <c r="G163">
+      <c r="H163">
         <v>1571</v>
       </c>
-      <c r="H163">
+      <c r="I163">
         <v>1661</v>
       </c>
-      <c r="I163">
+      <c r="J163">
         <v>1976</v>
       </c>
-      <c r="J163">
+      <c r="K163">
         <v>1977</v>
       </c>
-      <c r="K163">
+      <c r="L163">
         <v>1978</v>
       </c>
-      <c r="L163">
+      <c r="M163">
         <v>1979</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A164">
+        <v>163</v>
+      </c>
+      <c r="B164">
         <v>22</v>
       </c>
-      <c r="B164">
+      <c r="C164">
         <v>89</v>
       </c>
-      <c r="C164">
+      <c r="D164">
         <v>201</v>
       </c>
-      <c r="D164">
+      <c r="E164">
         <v>427</v>
       </c>
-      <c r="E164">
+      <c r="F164">
         <v>700</v>
       </c>
-      <c r="F164">
+      <c r="G164">
         <v>770</v>
       </c>
-      <c r="G164">
+      <c r="H164">
         <v>810</v>
       </c>
-      <c r="H164">
+      <c r="I164">
         <v>837</v>
       </c>
-      <c r="I164">
+      <c r="J164">
         <v>1196</v>
       </c>
-      <c r="J164">
+      <c r="K164">
         <v>1321</v>
       </c>
-      <c r="K164">
+      <c r="L164">
         <v>1430</v>
       </c>
-      <c r="L164">
+      <c r="M164">
         <v>1588</v>
       </c>
-      <c r="M164">
+      <c r="N164">
         <v>1771</v>
       </c>
-      <c r="N164">
+      <c r="O164">
         <v>1904</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165">
         <v>57</v>
       </c>
-      <c r="B165">
+      <c r="C165">
         <v>877</v>
       </c>
-      <c r="C165">
+      <c r="D165">
         <v>999</v>
       </c>
-      <c r="D165">
+      <c r="E165">
         <v>1105</v>
       </c>
-      <c r="E165">
+      <c r="F165">
         <v>1525</v>
       </c>
-      <c r="F165">
+      <c r="G165">
         <v>1614</v>
       </c>
-      <c r="G165">
+      <c r="H165">
         <v>1720</v>
       </c>
-      <c r="H165">
+      <c r="I165">
         <v>1737</v>
       </c>
-      <c r="I165">
+      <c r="J165">
         <v>1762</v>
       </c>
-      <c r="J165">
+      <c r="K165">
         <v>1799</v>
       </c>
-      <c r="K165">
+      <c r="L165">
         <v>1800</v>
       </c>
-      <c r="L165">
+      <c r="M165">
         <v>1844</v>
       </c>
-      <c r="M165">
+      <c r="N165">
         <v>1953</v>
       </c>
-      <c r="N165">
+      <c r="O165">
         <v>2053</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A166">
+        <v>165</v>
+      </c>
+      <c r="B166">
         <v>146</v>
       </c>
-      <c r="B166">
+      <c r="C166">
         <v>422</v>
       </c>
-      <c r="C166">
+      <c r="D166">
         <v>460</v>
       </c>
-      <c r="D166">
+      <c r="E166">
         <v>614</v>
       </c>
-      <c r="E166">
+      <c r="F166">
         <v>826</v>
       </c>
-      <c r="F166">
+      <c r="G166">
         <v>848</v>
       </c>
-      <c r="G166">
+      <c r="H166">
         <v>1041</v>
       </c>
-      <c r="H166">
+      <c r="I166">
         <v>1333</v>
       </c>
-      <c r="I166">
+      <c r="J166">
         <v>1365</v>
       </c>
-      <c r="J166">
+      <c r="K166">
         <v>1394</v>
       </c>
-      <c r="K166">
+      <c r="L166">
         <v>1898</v>
       </c>
-      <c r="L166">
+      <c r="M166">
         <v>1996</v>
       </c>
-      <c r="M166">
+      <c r="N166">
         <v>2021</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A167">
+        <v>166</v>
+      </c>
+      <c r="B167">
         <v>311</v>
       </c>
-      <c r="B167">
+      <c r="C167">
         <v>626</v>
       </c>
-      <c r="C167">
+      <c r="D167">
         <v>675</v>
       </c>
-      <c r="D167">
+      <c r="E167">
         <v>803</v>
       </c>
-      <c r="E167">
+      <c r="F167">
         <v>924</v>
       </c>
-      <c r="F167">
+      <c r="G167">
         <v>1125</v>
       </c>
-      <c r="G167">
+      <c r="H167">
         <v>1176</v>
       </c>
-      <c r="H167">
+      <c r="I167">
         <v>1252</v>
       </c>
-      <c r="I167">
+      <c r="J167">
         <v>1520</v>
       </c>
-      <c r="J167">
+      <c r="K167">
         <v>1873</v>
       </c>
-      <c r="K167">
+      <c r="L167">
         <v>1893</v>
       </c>
-      <c r="L167">
+      <c r="M167">
         <v>2100</v>
       </c>
-      <c r="M167">
+      <c r="N167">
         <v>2104</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A168">
+        <v>167</v>
+      </c>
+      <c r="B168">
         <v>161</v>
       </c>
-      <c r="B168">
+      <c r="C168">
         <v>314</v>
       </c>
-      <c r="C168">
+      <c r="D168">
         <v>358</v>
       </c>
-      <c r="D168">
+      <c r="E168">
         <v>428</v>
       </c>
-      <c r="E168">
+      <c r="F168">
         <v>479</v>
       </c>
-      <c r="F168">
+      <c r="G168">
         <v>699</v>
       </c>
-      <c r="G168">
+      <c r="H168">
         <v>743</v>
       </c>
-      <c r="H168">
+      <c r="I168">
         <v>760</v>
       </c>
-      <c r="I168">
+      <c r="J168">
         <v>800</v>
       </c>
-      <c r="J168">
+      <c r="K168">
         <v>918</v>
       </c>
-      <c r="K168">
+      <c r="L168">
         <v>1194</v>
       </c>
-      <c r="L168">
+      <c r="M168">
         <v>1276</v>
       </c>
-      <c r="M168">
+      <c r="N168">
         <v>1436</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A169">
+        <v>168</v>
+      </c>
+      <c r="B169">
         <v>471</v>
       </c>
-      <c r="B169">
+      <c r="C169">
         <v>577</v>
       </c>
-      <c r="C169">
+      <c r="D169">
         <v>593</v>
       </c>
-      <c r="D169">
+      <c r="E169">
         <v>634</v>
       </c>
-      <c r="E169">
+      <c r="F169">
         <v>665</v>
       </c>
-      <c r="F169">
+      <c r="G169">
         <v>853</v>
       </c>
-      <c r="G169">
+      <c r="H169">
         <v>908</v>
       </c>
-      <c r="H169">
+      <c r="I169">
         <v>1108</v>
       </c>
-      <c r="I169">
+      <c r="J169">
         <v>1425</v>
       </c>
-      <c r="J169">
+      <c r="K169">
         <v>1428</v>
       </c>
-      <c r="K169">
+      <c r="L169">
         <v>1455</v>
       </c>
-      <c r="L169">
+      <c r="M169">
         <v>1497</v>
       </c>
-      <c r="M169">
+      <c r="N169">
         <v>1566</v>
       </c>
-      <c r="N169">
+      <c r="O169">
         <v>1876</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A170">
+        <v>169</v>
+      </c>
+      <c r="B170">
         <v>281</v>
       </c>
-      <c r="B170">
+      <c r="C170">
         <v>459</v>
       </c>
-      <c r="C170">
+      <c r="D170">
         <v>463</v>
       </c>
-      <c r="D170">
+      <c r="E170">
         <v>854</v>
       </c>
-      <c r="E170">
+      <c r="F170">
         <v>1028</v>
       </c>
-      <c r="F170">
+      <c r="G170">
         <v>1067</v>
       </c>
-      <c r="G170">
+      <c r="H170">
         <v>1152</v>
       </c>
-      <c r="H170">
+      <c r="I170">
         <v>1157</v>
       </c>
-      <c r="I170">
+      <c r="J170">
         <v>1166</v>
       </c>
-      <c r="J170">
+      <c r="K170">
         <v>1878</v>
       </c>
-      <c r="K170">
+      <c r="L170">
         <v>1910</v>
       </c>
-      <c r="L170">
+      <c r="M170">
         <v>1966</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A171">
+        <v>170</v>
+      </c>
+      <c r="B171">
         <v>108</v>
       </c>
-      <c r="B171">
+      <c r="C171">
         <v>188</v>
       </c>
-      <c r="C171">
+      <c r="D171">
         <v>545</v>
       </c>
-      <c r="D171">
+      <c r="E171">
         <v>597</v>
       </c>
-      <c r="E171">
+      <c r="F171">
         <v>796</v>
       </c>
-      <c r="F171">
+      <c r="G171">
         <v>802</v>
       </c>
-      <c r="G171">
+      <c r="H171">
         <v>812</v>
       </c>
-      <c r="H171">
+      <c r="I171">
         <v>816</v>
       </c>
-      <c r="I171">
+      <c r="J171">
         <v>897</v>
       </c>
-      <c r="J171">
+      <c r="K171">
         <v>1012</v>
       </c>
-      <c r="K171">
+      <c r="L171">
         <v>1198</v>
       </c>
-      <c r="L171">
+      <c r="M171">
         <v>1938</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A172">
+        <v>171</v>
+      </c>
+      <c r="B172">
         <v>1051</v>
       </c>
-      <c r="B172">
+      <c r="C172">
         <v>1062</v>
       </c>
-      <c r="C172">
+      <c r="D172">
         <v>1063</v>
       </c>
-      <c r="D172">
+      <c r="E172">
         <v>1066</v>
       </c>
-      <c r="E172">
+      <c r="F172">
         <v>1073</v>
       </c>
-      <c r="F172">
+      <c r="G172">
         <v>1165</v>
       </c>
-      <c r="G172">
+      <c r="H172">
         <v>1211</v>
       </c>
-      <c r="H172">
+      <c r="I172">
         <v>1231</v>
       </c>
-      <c r="I172">
+      <c r="J172">
         <v>1242</v>
       </c>
-      <c r="J172">
+      <c r="K172">
         <v>1412</v>
       </c>
-      <c r="K172">
+      <c r="L172">
         <v>1681</v>
       </c>
-      <c r="L172">
+      <c r="M172">
         <v>1856</v>
       </c>
-      <c r="M172">
+      <c r="N172">
         <v>1887</v>
       </c>
-      <c r="N172">
+      <c r="O172">
         <v>1891</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="O173">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P173">
         <f>COUNTA(list[])</f>
-        <v>2105</v>
-      </c>
-    </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="O174">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P174">
         <f>MAX(list[])</f>
         <v>2107</v>
       </c>

--- a/p/utils/csv_table.xlsx
+++ b/p/utils/csv_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adsv\private\books\language\ingush\Dahkilgov\github\dahkilgov\p\utils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F513E2FA-453C-4841-A5EA-C88322803CDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE1F038-75F7-46C6-A8E2-5AE12693A7A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-2415" windowWidth="38640" windowHeight="21120" xr2:uid="{09FF60B3-0866-4FB8-9F4D-0BC30783F9C4}"/>
+    <workbookView xWindow="29040" yWindow="-2295" windowWidth="20805" windowHeight="20985" xr2:uid="{09FF60B3-0866-4FB8-9F4D-0BC30783F9C4}"/>
   </bookViews>
   <sheets>
     <sheet name="list" sheetId="2" r:id="rId1"/>
@@ -793,21 +793,24 @@
         <v>1230</v>
       </c>
       <c r="F7">
+        <v>1410</v>
+      </c>
+      <c r="G7">
         <v>1411</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>1471</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>1516</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>1607</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>1651</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>1868</v>
       </c>
     </row>
@@ -5197,7 +5200,7 @@
         <v>2106</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>112</v>
       </c>
@@ -5238,7 +5241,7 @@
         <v>1788</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>113</v>
       </c>
@@ -5282,7 +5285,7 @@
         <v>1707</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>114</v>
       </c>
@@ -5326,7 +5329,7 @@
         <v>1715</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>115</v>
       </c>
@@ -5367,7 +5370,7 @@
         <v>1949</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>116</v>
       </c>
@@ -5408,7 +5411,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>117</v>
       </c>
@@ -5449,7 +5452,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>118</v>
       </c>
@@ -5490,16 +5493,13 @@
         <v>1227</v>
       </c>
       <c r="N119">
-        <v>1410</v>
+        <v>2015</v>
       </c>
       <c r="O119">
-        <v>2015</v>
-      </c>
-      <c r="P119">
         <v>2073</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>119</v>
       </c>
@@ -5543,7 +5543,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>120</v>
       </c>
@@ -5587,7 +5587,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>121</v>
       </c>
@@ -5628,7 +5628,7 @@
         <v>1831</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>122</v>
       </c>
@@ -5669,7 +5669,7 @@
         <v>2054</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>123</v>
       </c>
@@ -5710,7 +5710,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>124</v>
       </c>
@@ -5754,7 +5754,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>125</v>
       </c>
@@ -5795,7 +5795,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>126</v>
       </c>
@@ -5839,7 +5839,7 @@
         <v>1931</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>127</v>
       </c>
